--- a/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,212 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21603200</v>
+        <v>22594400</v>
       </c>
       <c r="E8" s="3">
-        <v>20657500</v>
+        <v>21928600</v>
       </c>
       <c r="F8" s="3">
-        <v>23662300</v>
+        <v>20968600</v>
       </c>
       <c r="G8" s="3">
-        <v>21821800</v>
+        <v>24018700</v>
       </c>
       <c r="H8" s="3">
-        <v>21362900</v>
+        <v>22150500</v>
       </c>
       <c r="I8" s="3">
-        <v>20377300</v>
+        <v>21684600</v>
       </c>
       <c r="J8" s="3">
+        <v>20684200</v>
+      </c>
+      <c r="K8" s="3">
         <v>21468600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20854400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21594500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21260400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22730300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22185300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22940800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>23597900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26753500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27085300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27332100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26705400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29643300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28339000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27316900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>25931300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27821100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27624000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>26057300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25390800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>26880700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>25156800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>24903300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -931,29 +937,32 @@
       <c r="Y9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA9" s="3">
         <v>14315900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13646700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12122500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11756500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14418700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12033700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11724700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1023,29 +1032,32 @@
       <c r="Y10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA10" s="3">
         <v>13505200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>13977300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13934700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13634400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>12462000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13123100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13178600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1078,8 +1090,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1170,8 +1183,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,192 +1278,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>180600</v>
+        <v>134100</v>
       </c>
       <c r="E14" s="3">
-        <v>169700</v>
+        <v>183300</v>
       </c>
       <c r="F14" s="3">
-        <v>435400</v>
+        <v>172300</v>
       </c>
       <c r="G14" s="3">
-        <v>142200</v>
+        <v>441900</v>
       </c>
       <c r="H14" s="3">
-        <v>170800</v>
+        <v>144400</v>
       </c>
       <c r="I14" s="3">
-        <v>145200</v>
+        <v>173400</v>
       </c>
       <c r="J14" s="3">
+        <v>147400</v>
+      </c>
+      <c r="K14" s="3">
         <v>608900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>171800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>188300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>638700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>328000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>203600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>184200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>886600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>316400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>277500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>207800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1326000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>957400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>300900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>243400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>167300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2970900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>332400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>246800</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2647100</v>
+        <v>2743700</v>
       </c>
       <c r="E15" s="3">
-        <v>2630400</v>
+        <v>2687000</v>
       </c>
       <c r="F15" s="3">
-        <v>2695500</v>
+        <v>2670000</v>
       </c>
       <c r="G15" s="3">
-        <v>2625200</v>
+        <v>2736100</v>
       </c>
       <c r="H15" s="3">
-        <v>2600700</v>
+        <v>2664700</v>
       </c>
       <c r="I15" s="3">
-        <v>2587200</v>
+        <v>2639900</v>
       </c>
       <c r="J15" s="3">
+        <v>2626200</v>
+      </c>
+      <c r="K15" s="3">
         <v>2677800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2667600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2791000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2811400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2735500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2782000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2910000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3141000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3330600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3326500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3323100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3302300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3296200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3154600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3074900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2958700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3108500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>6102700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5974800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5995600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3364800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3683200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3208700</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1477,192 +1502,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18440600</v>
+        <v>18986900</v>
       </c>
       <c r="E17" s="3">
-        <v>17505800</v>
+        <v>18718300</v>
       </c>
       <c r="F17" s="3">
-        <v>21616100</v>
+        <v>17769500</v>
       </c>
       <c r="G17" s="3">
-        <v>18340500</v>
+        <v>21941700</v>
       </c>
       <c r="H17" s="3">
-        <v>18088200</v>
+        <v>18616700</v>
       </c>
       <c r="I17" s="3">
-        <v>17035000</v>
+        <v>18360600</v>
       </c>
       <c r="J17" s="3">
+        <v>17291600</v>
+      </c>
+      <c r="K17" s="3">
         <v>19948500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17210600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17823700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17686300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21531600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18566100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18960200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19353500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25769300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22825300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22942900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22077800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28041200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24030900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22360500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21047900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24898500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24267800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21413500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>20647900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24918300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21679200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21008600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3162600</v>
+        <v>3607500</v>
       </c>
       <c r="E18" s="3">
-        <v>3151700</v>
+        <v>3210200</v>
       </c>
       <c r="F18" s="3">
-        <v>2046200</v>
+        <v>3199100</v>
       </c>
       <c r="G18" s="3">
-        <v>3481300</v>
+        <v>2077000</v>
       </c>
       <c r="H18" s="3">
-        <v>3274800</v>
+        <v>3533700</v>
       </c>
       <c r="I18" s="3">
-        <v>3342300</v>
+        <v>3324100</v>
       </c>
       <c r="J18" s="3">
+        <v>3392600</v>
+      </c>
+      <c r="K18" s="3">
         <v>1520100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3643800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3770800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3574100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1198700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3619200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3980600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4244400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>984300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4260000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4389200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4627600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1602100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4308200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4956500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4883400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2922500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3356200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4643800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4742900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1962400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3477700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3894700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1695,192 +1727,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-97800</v>
+        <v>-118000</v>
       </c>
       <c r="E20" s="3">
-        <v>683200</v>
+        <v>-99300</v>
       </c>
       <c r="F20" s="3">
-        <v>-135400</v>
+        <v>693500</v>
       </c>
       <c r="G20" s="3">
-        <v>-91800</v>
+        <v>-137400</v>
       </c>
       <c r="H20" s="3">
-        <v>4800</v>
+        <v>-93200</v>
       </c>
       <c r="I20" s="3">
-        <v>147300</v>
+        <v>4900</v>
       </c>
       <c r="J20" s="3">
+        <v>149500</v>
+      </c>
+      <c r="K20" s="3">
         <v>83900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>56800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-28800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>73600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-82200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-27200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-82500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-15500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>197800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-242800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-40300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>19900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>49300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1123500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>78400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>103800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>79200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>236000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>190600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5711900</v>
+        <v>6233200</v>
       </c>
       <c r="E21" s="3">
-        <v>6465300</v>
+        <v>5797900</v>
       </c>
       <c r="F21" s="3">
-        <v>4606300</v>
+        <v>6562600</v>
       </c>
       <c r="G21" s="3">
-        <v>6014700</v>
+        <v>4675700</v>
       </c>
       <c r="H21" s="3">
-        <v>5880300</v>
+        <v>6105200</v>
       </c>
       <c r="I21" s="3">
-        <v>6076800</v>
+        <v>5968800</v>
       </c>
       <c r="J21" s="3">
+        <v>6168300</v>
+      </c>
+      <c r="K21" s="3">
         <v>4281800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6368300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6533100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6459100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3852000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6373900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6870900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7377200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4232300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7571100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7689000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8127700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4655400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7422400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8051200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7891400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5939100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7548400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7734900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7838500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5406400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6963800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7254300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1932,8 +1971,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
@@ -1950,213 +1989,222 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>62500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>78700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>74500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>75300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>85100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>74400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3064800</v>
+        <v>3489600</v>
       </c>
       <c r="E23" s="3">
-        <v>3834800</v>
+        <v>3111000</v>
       </c>
       <c r="F23" s="3">
-        <v>1910800</v>
+        <v>3892600</v>
       </c>
       <c r="G23" s="3">
-        <v>3389400</v>
+        <v>1939600</v>
       </c>
       <c r="H23" s="3">
-        <v>3279600</v>
+        <v>3440500</v>
       </c>
       <c r="I23" s="3">
-        <v>3489600</v>
+        <v>3329000</v>
       </c>
       <c r="J23" s="3">
+        <v>3542100</v>
+      </c>
+      <c r="K23" s="3">
         <v>1604000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3700600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3742100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3647700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1116500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3591900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3960800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4236200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>901800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4244600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4365900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4825300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1359200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4267900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4976300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4932700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2841400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4401100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4647600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4771400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1956500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3639300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3998600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1024300</v>
+        <v>1081400</v>
       </c>
       <c r="E24" s="3">
-        <v>1244100</v>
+        <v>1039700</v>
       </c>
       <c r="F24" s="3">
-        <v>618300</v>
+        <v>1262900</v>
       </c>
       <c r="G24" s="3">
-        <v>1018500</v>
+        <v>627600</v>
       </c>
       <c r="H24" s="3">
-        <v>950600</v>
+        <v>1033900</v>
       </c>
       <c r="I24" s="3">
-        <v>898100</v>
+        <v>964900</v>
       </c>
       <c r="J24" s="3">
+        <v>911600</v>
+      </c>
+      <c r="K24" s="3">
         <v>473200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1142600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1165700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1030900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>507000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1055300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1246800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1272500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>152100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1332200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1217500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1491500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>365800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1302600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1763500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1520700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>761900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1444900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1463800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1466700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>386100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1271900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1264100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2247,192 +2295,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2040500</v>
+        <v>2408100</v>
       </c>
       <c r="E26" s="3">
-        <v>2590700</v>
+        <v>2071200</v>
       </c>
       <c r="F26" s="3">
-        <v>1292500</v>
+        <v>2629700</v>
       </c>
       <c r="G26" s="3">
-        <v>2370900</v>
+        <v>1311900</v>
       </c>
       <c r="H26" s="3">
-        <v>2329000</v>
+        <v>2406600</v>
       </c>
       <c r="I26" s="3">
-        <v>2591500</v>
+        <v>2364100</v>
       </c>
       <c r="J26" s="3">
+        <v>2630500</v>
+      </c>
+      <c r="K26" s="3">
         <v>1130800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2558000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2576300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2616800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>609500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2536600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2714000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2963700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>749700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2912400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3148500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3333900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>993500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2965200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3212800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3412000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2079500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2956200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3183800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3304700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1570400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2367400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2734400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1959300</v>
+        <v>2293400</v>
       </c>
       <c r="E27" s="3">
-        <v>2495100</v>
+        <v>1988800</v>
       </c>
       <c r="F27" s="3">
-        <v>1199100</v>
+        <v>2532700</v>
       </c>
       <c r="G27" s="3">
-        <v>2230500</v>
+        <v>1217200</v>
       </c>
       <c r="H27" s="3">
-        <v>2178200</v>
+        <v>2264100</v>
       </c>
       <c r="I27" s="3">
-        <v>2447300</v>
+        <v>2211000</v>
       </c>
       <c r="J27" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="K27" s="3">
         <v>1000900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2435500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2421400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2498900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>602700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2123200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2094500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2325600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>514400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2270700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2455000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2569700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>600000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2193900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2508100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2633800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1564900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2012000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2512900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2647500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1165500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1708600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2523,8 +2580,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2615,8 +2675,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2707,8 +2770,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2799,192 +2865,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>97800</v>
+        <v>118000</v>
       </c>
       <c r="E32" s="3">
-        <v>-683200</v>
+        <v>99300</v>
       </c>
       <c r="F32" s="3">
-        <v>135400</v>
+        <v>-693500</v>
       </c>
       <c r="G32" s="3">
-        <v>91800</v>
+        <v>137400</v>
       </c>
       <c r="H32" s="3">
-        <v>-4800</v>
+        <v>93200</v>
       </c>
       <c r="I32" s="3">
-        <v>-147300</v>
+        <v>-4900</v>
       </c>
       <c r="J32" s="3">
+        <v>-149500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-83900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-56800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>28800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-73600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>82200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>27200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>19800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>82500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>15500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-197800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>242800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>40300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-19900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-49300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>18700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1123500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-78400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-103800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-190600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1959300</v>
+        <v>2293400</v>
       </c>
       <c r="E33" s="3">
-        <v>2495100</v>
+        <v>1988800</v>
       </c>
       <c r="F33" s="3">
-        <v>1199100</v>
+        <v>2532700</v>
       </c>
       <c r="G33" s="3">
-        <v>2230500</v>
+        <v>1217200</v>
       </c>
       <c r="H33" s="3">
-        <v>2178200</v>
+        <v>2264100</v>
       </c>
       <c r="I33" s="3">
-        <v>2447300</v>
+        <v>2211000</v>
       </c>
       <c r="J33" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="K33" s="3">
         <v>1000900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2435500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2421400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2498900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>602700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2123200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2094500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2325600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>514400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2270700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2455000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2569700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>600000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2193900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2508100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2633800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1564900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2012000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2512900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2647500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1165500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1708600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3075,197 +3150,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1959300</v>
+        <v>2293400</v>
       </c>
       <c r="E35" s="3">
-        <v>2495100</v>
+        <v>1988800</v>
       </c>
       <c r="F35" s="3">
-        <v>1199100</v>
+        <v>2532700</v>
       </c>
       <c r="G35" s="3">
-        <v>2230500</v>
+        <v>1217200</v>
       </c>
       <c r="H35" s="3">
-        <v>2178200</v>
+        <v>2264100</v>
       </c>
       <c r="I35" s="3">
-        <v>2447300</v>
+        <v>2211000</v>
       </c>
       <c r="J35" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="K35" s="3">
         <v>1000900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2435500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2421400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2498900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>602700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2123200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2094500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2325600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>514400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2270700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2455000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2569700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>600000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2193900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2508100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2633800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1564900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2012000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2512900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2647500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1165500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1708600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3298,8 +3382,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3332,836 +3417,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4747700</v>
+        <v>6369600</v>
       </c>
       <c r="E41" s="3">
-        <v>6758900</v>
+        <v>4819200</v>
       </c>
       <c r="F41" s="3">
-        <v>5271600</v>
+        <v>6860700</v>
       </c>
       <c r="G41" s="3">
-        <v>5457000</v>
+        <v>5351000</v>
       </c>
       <c r="H41" s="3">
-        <v>6300100</v>
+        <v>5539100</v>
       </c>
       <c r="I41" s="3">
-        <v>6140200</v>
+        <v>6395000</v>
       </c>
       <c r="J41" s="3">
+        <v>6232700</v>
+      </c>
+      <c r="K41" s="3">
         <v>5541500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5677100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6526600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8373800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6634300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9916700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7839400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9148700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9105800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7975500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8527900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9356900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9092300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8575100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8264800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7245700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15144700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6929900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7599600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8690400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8206600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5897100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8998400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>777100</v>
+        <v>729600</v>
       </c>
       <c r="E42" s="3">
-        <v>817900</v>
+        <v>788800</v>
       </c>
       <c r="F42" s="3">
-        <v>655100</v>
+        <v>830200</v>
       </c>
       <c r="G42" s="3">
-        <v>715100</v>
+        <v>664900</v>
       </c>
       <c r="H42" s="3">
-        <v>842700</v>
+        <v>725800</v>
       </c>
       <c r="I42" s="3">
-        <v>745100</v>
+        <v>855400</v>
       </c>
       <c r="J42" s="3">
+        <v>756300</v>
+      </c>
+      <c r="K42" s="3">
         <v>587200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>352000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>381600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>442400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>295900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4437100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5884200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>305000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>285300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1174300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1041400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>998300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1131600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1158300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1087400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1160200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1401100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>398600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1303600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>786800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>566300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>677900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>28652600</v>
+        <v>30136100</v>
       </c>
       <c r="E43" s="3">
-        <v>25740400</v>
+        <v>29084100</v>
       </c>
       <c r="F43" s="3">
-        <v>27797500</v>
+        <v>26128100</v>
       </c>
       <c r="G43" s="3">
-        <v>27183300</v>
+        <v>28216200</v>
       </c>
       <c r="H43" s="3">
-        <v>23637800</v>
+        <v>27592700</v>
       </c>
       <c r="I43" s="3">
-        <v>22118700</v>
+        <v>23993800</v>
       </c>
       <c r="J43" s="3">
+        <v>22451800</v>
+      </c>
+      <c r="K43" s="3">
         <v>23936900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24668900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21499000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22885100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25060000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27566200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25444000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27582500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>30860000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>41217200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>37411000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>38645800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>42201700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>39166800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>36843100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>34757800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>68781300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>31235300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>29446200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26375400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>27995700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>29108000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25063000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3727600</v>
+        <v>3773100</v>
       </c>
       <c r="E44" s="3">
-        <v>3709100</v>
+        <v>3783700</v>
       </c>
       <c r="F44" s="3">
-        <v>3435600</v>
+        <v>3765000</v>
       </c>
       <c r="G44" s="3">
-        <v>3292200</v>
+        <v>3487300</v>
       </c>
       <c r="H44" s="3">
-        <v>3135900</v>
+        <v>3341800</v>
       </c>
       <c r="I44" s="3">
-        <v>2793200</v>
+        <v>3183100</v>
       </c>
       <c r="J44" s="3">
+        <v>2835300</v>
+      </c>
+      <c r="K44" s="3">
         <v>2711500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2416000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2386300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2433500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2236400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2641700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2363200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2630700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2267100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2818000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2453800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2786700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3187000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4045200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3198000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3250000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6759800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4153400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3497200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3655500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3240900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3875200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3907300</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8081400</v>
+        <v>7687200</v>
       </c>
       <c r="E45" s="3">
-        <v>9241100</v>
+        <v>8203100</v>
       </c>
       <c r="F45" s="3">
-        <v>7028500</v>
+        <v>9380300</v>
       </c>
       <c r="G45" s="3">
-        <v>7676900</v>
+        <v>7134400</v>
       </c>
       <c r="H45" s="3">
-        <v>7714500</v>
+        <v>7792500</v>
       </c>
       <c r="I45" s="3">
-        <v>7635400</v>
+        <v>7830700</v>
       </c>
       <c r="J45" s="3">
+        <v>7750300</v>
+      </c>
+      <c r="K45" s="3">
         <v>5181000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4959400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4924400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5208500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3537400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4778900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4897300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17876500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16539700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5436400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5317700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6432000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7620800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7330500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7113200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5420500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9493000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5634700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5426600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6214100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7111600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7980800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7524600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>45986200</v>
+        <v>48695600</v>
       </c>
       <c r="E46" s="3">
-        <v>46267400</v>
+        <v>46678800</v>
       </c>
       <c r="F46" s="3">
-        <v>44188300</v>
+        <v>46964200</v>
       </c>
       <c r="G46" s="3">
-        <v>44324500</v>
+        <v>44853800</v>
       </c>
       <c r="H46" s="3">
-        <v>41631100</v>
+        <v>44992000</v>
       </c>
       <c r="I46" s="3">
-        <v>39432500</v>
+        <v>42258100</v>
       </c>
       <c r="J46" s="3">
+        <v>40026400</v>
+      </c>
+      <c r="K46" s="3">
         <v>37958200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38073500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35717900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39343300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37764000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>49340600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>46428000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>57543400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>59057800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>58621500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>54751800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>58219800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>63233500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>60275800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>56506500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>51834100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>53057200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>48351800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>47273300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>45722100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>47121200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47539100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>46264000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>14605400</v>
+        <v>15281900</v>
       </c>
       <c r="E47" s="3">
-        <v>13230300</v>
+        <v>14825400</v>
       </c>
       <c r="F47" s="3">
-        <v>11207700</v>
+        <v>13429500</v>
       </c>
       <c r="G47" s="3">
-        <v>12680600</v>
+        <v>11376400</v>
       </c>
       <c r="H47" s="3">
-        <v>13168300</v>
+        <v>12871600</v>
       </c>
       <c r="I47" s="3">
-        <v>12946700</v>
+        <v>13366700</v>
       </c>
       <c r="J47" s="3">
+        <v>13141700</v>
+      </c>
+      <c r="K47" s="3">
         <v>12323600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13565400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14417400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14328900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13662100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13548000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13074400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12768700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9951600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14218700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13411900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13511100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13807300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13538500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13687300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14984100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>23831700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9577600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>9086300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8923400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8691600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8571600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8135900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>79647500</v>
+        <v>81320900</v>
       </c>
       <c r="E48" s="3">
-        <v>78254100</v>
+        <v>80847000</v>
       </c>
       <c r="F48" s="3">
-        <v>77543400</v>
+        <v>79432600</v>
       </c>
       <c r="G48" s="3">
-        <v>75285700</v>
+        <v>78711200</v>
       </c>
       <c r="H48" s="3">
-        <v>75500000</v>
+        <v>76419500</v>
       </c>
       <c r="I48" s="3">
-        <v>75228000</v>
+        <v>76637100</v>
       </c>
       <c r="J48" s="3">
+        <v>76361000</v>
+      </c>
+      <c r="K48" s="3">
         <v>74753100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>77189000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>80463700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>82028500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>78731800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>79668500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>84222100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>91460600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>93742200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>95995400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>96175900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>95402300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>95907300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>92625800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>91769200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>89134300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>177505500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>87753100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>88621500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>87913000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>86207700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>84650400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>83893100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>25377100</v>
+        <v>25946000</v>
       </c>
       <c r="E49" s="3">
-        <v>23396200</v>
+        <v>25759300</v>
       </c>
       <c r="F49" s="3">
-        <v>22618000</v>
+        <v>23748600</v>
       </c>
       <c r="G49" s="3">
-        <v>22151000</v>
+        <v>22958600</v>
       </c>
       <c r="H49" s="3">
-        <v>22176700</v>
+        <v>22484600</v>
       </c>
       <c r="I49" s="3">
-        <v>21734200</v>
+        <v>22510700</v>
       </c>
       <c r="J49" s="3">
+        <v>22061500</v>
+      </c>
+      <c r="K49" s="3">
         <v>21014500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>20859600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20768100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21166700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20008300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19726800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20619900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22665300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23565900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>24100000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23505500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23186600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>24162400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23906500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23809200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23033500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>48621500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>26804000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>26981900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>26837400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>26415300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>25833000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>23543700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4252,8 +4365,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4344,100 +4460,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12425800</v>
+        <v>12384900</v>
       </c>
       <c r="E52" s="3">
-        <v>12362100</v>
+        <v>12613000</v>
       </c>
       <c r="F52" s="3">
-        <v>12493400</v>
+        <v>12548300</v>
       </c>
       <c r="G52" s="3">
-        <v>12594500</v>
+        <v>12681600</v>
       </c>
       <c r="H52" s="3">
-        <v>12739200</v>
+        <v>12784200</v>
       </c>
       <c r="I52" s="3">
-        <v>12696600</v>
+        <v>12931000</v>
       </c>
       <c r="J52" s="3">
+        <v>12887800</v>
+      </c>
+      <c r="K52" s="3">
         <v>12396000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12062300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12440600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12789200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12659100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12624700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13703800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15336600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16437000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16063700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16481200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16408400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17145900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16387700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16004400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16148700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>30822500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>22127200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22380200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22405700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20054600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>19890900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4528,100 +4650,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>178042200</v>
+        <v>183629300</v>
       </c>
       <c r="E54" s="3">
-        <v>173510200</v>
+        <v>180723500</v>
       </c>
       <c r="F54" s="3">
-        <v>168050800</v>
+        <v>176123300</v>
       </c>
       <c r="G54" s="3">
-        <v>167036300</v>
+        <v>170581700</v>
       </c>
       <c r="H54" s="3">
-        <v>165215400</v>
+        <v>169551900</v>
       </c>
       <c r="I54" s="3">
-        <v>162038000</v>
+        <v>167703600</v>
       </c>
       <c r="J54" s="3">
+        <v>164478300</v>
+      </c>
+      <c r="K54" s="3">
         <v>158445300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>161749700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>163807600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>169656600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>162825300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>174908600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>178048300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>199774600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>202754500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>208999200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>204326400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>206728300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>214256400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>206734400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>201776600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>195134800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>194734700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>194613800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>194343300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>191801600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>188490400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>186485000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>181367100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4654,8 +4782,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4688,560 +4817,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>16045500</v>
+        <v>17215400</v>
       </c>
       <c r="E57" s="3">
-        <v>16683800</v>
+        <v>16287200</v>
       </c>
       <c r="F57" s="3">
-        <v>7374000</v>
+        <v>16935100</v>
       </c>
       <c r="G57" s="3">
-        <v>16508400</v>
+        <v>7485000</v>
       </c>
       <c r="H57" s="3">
-        <v>14771600</v>
+        <v>16757100</v>
       </c>
       <c r="I57" s="3">
-        <v>15867200</v>
+        <v>14994100</v>
       </c>
       <c r="J57" s="3">
+        <v>16106200</v>
+      </c>
+      <c r="K57" s="3">
         <v>6541500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14575100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13308600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14666400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16709000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22680600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13558800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15530900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18877600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15531100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15365600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15442400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>20108700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15250500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13794100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13731500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>16378000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12341800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11209100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10462900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14307300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10823200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10149200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>15645000</v>
+        <v>20043900</v>
       </c>
       <c r="E58" s="3">
-        <v>18765600</v>
+        <v>15880600</v>
       </c>
       <c r="F58" s="3">
-        <v>13581800</v>
+        <v>19048300</v>
       </c>
       <c r="G58" s="3">
-        <v>18577800</v>
+        <v>13786400</v>
       </c>
       <c r="H58" s="3">
-        <v>16460800</v>
+        <v>18857500</v>
       </c>
       <c r="I58" s="3">
-        <v>14885500</v>
+        <v>16708700</v>
       </c>
       <c r="J58" s="3">
+        <v>15109700</v>
+      </c>
+      <c r="K58" s="3">
         <v>12193000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14723800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16253200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>28766600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>23840300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>38403300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18080500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>21988600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>19458000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21904900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>16681400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>18869500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>13565300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15598300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10476900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>14238400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15416900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8838000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>8994300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>9532100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8191800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9374100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6176000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13391300</v>
+        <v>12483100</v>
       </c>
       <c r="E59" s="3">
-        <v>12243300</v>
+        <v>13593000</v>
       </c>
       <c r="F59" s="3">
-        <v>24461700</v>
+        <v>12427700</v>
       </c>
       <c r="G59" s="3">
-        <v>11039800</v>
+        <v>24830100</v>
       </c>
       <c r="H59" s="3">
-        <v>11768300</v>
+        <v>11206100</v>
       </c>
       <c r="I59" s="3">
-        <v>11107000</v>
+        <v>11945600</v>
       </c>
       <c r="J59" s="3">
+        <v>11274200</v>
+      </c>
+      <c r="K59" s="3">
         <v>22822800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10907200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11452200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10987400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12102100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10978900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12298300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17491000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19877400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13620000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14530600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14313800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16567700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14876600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15946100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14009300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19934300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14207200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14711400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15808300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14146400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14897400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13836100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>45081900</v>
+        <v>49742400</v>
       </c>
       <c r="E60" s="3">
-        <v>47692700</v>
+        <v>45760800</v>
       </c>
       <c r="F60" s="3">
-        <v>45417500</v>
+        <v>48411000</v>
       </c>
       <c r="G60" s="3">
-        <v>46126000</v>
+        <v>46101500</v>
       </c>
       <c r="H60" s="3">
-        <v>43000700</v>
+        <v>46820700</v>
       </c>
       <c r="I60" s="3">
-        <v>41859600</v>
+        <v>43648300</v>
       </c>
       <c r="J60" s="3">
+        <v>42490100</v>
+      </c>
+      <c r="K60" s="3">
         <v>41557400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40206000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41014000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>54420400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>52651500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>72062700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>43937600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>55010500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>58213100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>51055900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>46577600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>48625600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>50241800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>45725300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>40217100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>41979300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>41786800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>35387100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34914900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>35803300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>36645500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>35094700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>30161200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51390400</v>
+        <v>51825400</v>
       </c>
       <c r="E61" s="3">
-        <v>47680700</v>
+        <v>52164300</v>
       </c>
       <c r="F61" s="3">
-        <v>47177700</v>
+        <v>48398800</v>
       </c>
       <c r="G61" s="3">
-        <v>44793700</v>
+        <v>47888200</v>
       </c>
       <c r="H61" s="3">
-        <v>45653400</v>
+        <v>45468300</v>
       </c>
       <c r="I61" s="3">
-        <v>43735300</v>
+        <v>46340900</v>
       </c>
       <c r="J61" s="3">
+        <v>44393900</v>
+      </c>
+      <c r="K61" s="3">
         <v>42318000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>45383600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>43143200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36398100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>35517800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25696600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19853800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23192800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>22413700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29780700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29372500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29574300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>27844600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>27448700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27278100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>25389200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28423700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28726400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28965100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>29015900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28331200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>29049600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>30307400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13708000</v>
+        <v>13848400</v>
       </c>
       <c r="E62" s="3">
-        <v>13148600</v>
+        <v>13914500</v>
       </c>
       <c r="F62" s="3">
-        <v>13367400</v>
+        <v>13346600</v>
       </c>
       <c r="G62" s="3">
-        <v>15019500</v>
+        <v>13568700</v>
       </c>
       <c r="H62" s="3">
-        <v>14845400</v>
+        <v>15245700</v>
       </c>
       <c r="I62" s="3">
-        <v>14728000</v>
+        <v>15068900</v>
       </c>
       <c r="J62" s="3">
+        <v>14949800</v>
+      </c>
+      <c r="K62" s="3">
         <v>14689500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16384400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16927600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17223600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16496500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18169400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18967200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20608700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21142000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22174100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22177200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21883800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22726000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22825400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22206200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21740200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>40355000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>21606000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>21475400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21294000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>20989200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21797200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21685400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5332,8 +5480,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5424,8 +5575,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5516,100 +5670,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>116177900</v>
+        <v>121391100</v>
       </c>
       <c r="E66" s="3">
-        <v>114098900</v>
+        <v>117927600</v>
       </c>
       <c r="F66" s="3">
-        <v>111203400</v>
+        <v>115817300</v>
       </c>
       <c r="G66" s="3">
-        <v>111092800</v>
+        <v>112878100</v>
       </c>
       <c r="H66" s="3">
-        <v>108971400</v>
+        <v>112765900</v>
       </c>
       <c r="I66" s="3">
-        <v>105502800</v>
+        <v>110612500</v>
       </c>
       <c r="J66" s="3">
+        <v>107091700</v>
+      </c>
+      <c r="K66" s="3">
         <v>103449800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>106805100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106011600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112803600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>109205700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>120390100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102256800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>119437400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>122926200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>125660600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>121280500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>123114000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>125220500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>119475700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>114165700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>112192700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>112807400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>109849800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>108990500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>108974100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>108194900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>107689800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>103690600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5642,8 +5802,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5734,8 +5895,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5826,8 +5990,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5918,8 +6085,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6010,100 +6180,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>57176900</v>
+        <v>58843400</v>
       </c>
       <c r="E72" s="3">
-        <v>55220300</v>
+        <v>58038000</v>
       </c>
       <c r="F72" s="3">
-        <v>54116800</v>
+        <v>56051900</v>
       </c>
       <c r="G72" s="3">
-        <v>52183500</v>
+        <v>54931800</v>
       </c>
       <c r="H72" s="3">
-        <v>51583100</v>
+        <v>52969400</v>
       </c>
       <c r="I72" s="3">
-        <v>49420100</v>
+        <v>52360000</v>
       </c>
       <c r="J72" s="3">
+        <v>50164300</v>
+      </c>
+      <c r="K72" s="3">
         <v>48431600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>47910400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>54408400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52990500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>50112200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50282400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53498600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>56283300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>57264500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>58586300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>58367600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>55697400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>57220900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>55878100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>54359500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>57216800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>55490700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>55074400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>54544700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>52229600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>49904000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>48738500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>48114000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6194,8 +6370,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6286,8 +6465,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6378,100 +6560,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>61864200</v>
+        <v>62238200</v>
       </c>
       <c r="E76" s="3">
-        <v>59411300</v>
+        <v>62795900</v>
       </c>
       <c r="F76" s="3">
-        <v>56847400</v>
+        <v>60306000</v>
       </c>
       <c r="G76" s="3">
-        <v>55943500</v>
+        <v>57703500</v>
       </c>
       <c r="H76" s="3">
-        <v>56244000</v>
+        <v>56786100</v>
       </c>
       <c r="I76" s="3">
-        <v>56535200</v>
+        <v>57091100</v>
       </c>
       <c r="J76" s="3">
+        <v>57386700</v>
+      </c>
+      <c r="K76" s="3">
         <v>54995500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>54944700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>57796000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>56853100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53619600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>54518600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75791500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80337200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>79828300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>83338500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>83045900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>83614300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>89035800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>87258700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>87610900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>82942000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>81927300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>84764000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>85352800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>82827500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>80295500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>78795200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>77676600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6562,197 +6750,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1959300</v>
+        <v>2293400</v>
       </c>
       <c r="E81" s="3">
-        <v>2495100</v>
+        <v>1988800</v>
       </c>
       <c r="F81" s="3">
-        <v>1199100</v>
+        <v>2532700</v>
       </c>
       <c r="G81" s="3">
-        <v>2230500</v>
+        <v>1217200</v>
       </c>
       <c r="H81" s="3">
-        <v>2178200</v>
+        <v>2264100</v>
       </c>
       <c r="I81" s="3">
-        <v>2447300</v>
+        <v>2211000</v>
       </c>
       <c r="J81" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="K81" s="3">
         <v>1000900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2435500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2421400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2498900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>602700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2123200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2094500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2325600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>514400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2270700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2455000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2569700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>600000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2193900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2508100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2633800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1564900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2012000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2512900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2647500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1165500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1708600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6785,100 +6982,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2647100</v>
+        <v>2743700</v>
       </c>
       <c r="E83" s="3">
-        <v>2630400</v>
+        <v>2687000</v>
       </c>
       <c r="F83" s="3">
-        <v>2695500</v>
+        <v>2670000</v>
       </c>
       <c r="G83" s="3">
-        <v>2625200</v>
+        <v>2736100</v>
       </c>
       <c r="H83" s="3">
-        <v>2600700</v>
+        <v>2664700</v>
       </c>
       <c r="I83" s="3">
-        <v>2587200</v>
+        <v>2639900</v>
       </c>
       <c r="J83" s="3">
+        <v>2626200</v>
+      </c>
+      <c r="K83" s="3">
         <v>2677800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2667600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2791000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2811400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2735500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2782000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2910000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3141000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3330600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3326500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3323100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3302300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3296200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3154600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3074900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2958700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3035200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3068600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3000700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3003800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3364800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3250100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3169000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6969,8 +7170,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7061,8 +7265,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7153,8 +7360,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7245,8 +7455,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7337,100 +7550,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3220600</v>
+        <v>4088800</v>
       </c>
       <c r="E89" s="3">
-        <v>2263400</v>
+        <v>3269100</v>
       </c>
       <c r="F89" s="3">
-        <v>7471700</v>
+        <v>2297500</v>
       </c>
       <c r="G89" s="3">
-        <v>2185600</v>
+        <v>7584200</v>
       </c>
       <c r="H89" s="3">
-        <v>2612400</v>
+        <v>2218600</v>
       </c>
       <c r="I89" s="3">
-        <v>2743400</v>
+        <v>2651700</v>
       </c>
       <c r="J89" s="3">
+        <v>2784700</v>
+      </c>
+      <c r="K89" s="3">
         <v>7526700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2660500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6647700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4170800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9295200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2983500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6301300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4112300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11279800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1644300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9735800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4350900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7673800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3773500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7209000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3926000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7650900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6131900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5252800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4754300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10658100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2885700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7551100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7463,100 +7682,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-502925000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-404987000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-537194000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-537220000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-430425000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-357543000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-526691000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-463257000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400176000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-378841000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3790900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3311400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3036100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2832700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4693900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4336700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3957900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3333700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5192700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4354400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3592000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3450900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4247500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2610700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2900200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2538600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3781500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3982200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3701000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2945900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7647,8 +7870,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7739,100 +7965,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4156300</v>
+        <v>-3717400</v>
       </c>
       <c r="E94" s="3">
-        <v>-2993100</v>
+        <v>-4218900</v>
       </c>
       <c r="F94" s="3">
-        <v>-2924200</v>
+        <v>-3038200</v>
       </c>
       <c r="G94" s="3">
-        <v>-3157600</v>
+        <v>-2968200</v>
       </c>
       <c r="H94" s="3">
-        <v>-2430300</v>
+        <v>-3205200</v>
       </c>
       <c r="I94" s="3">
-        <v>-3021000</v>
+        <v>-2466900</v>
       </c>
       <c r="J94" s="3">
+        <v>-3066500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1908500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2988300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2805200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4319400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>606900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2416900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2929600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4854000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4785300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3642300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3482200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4604300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3669900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3349400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4960500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4575200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2977700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3913400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5183400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4066000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6691400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3502400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7865,100 +8097,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-1434300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1358700</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-1379200</v>
       </c>
       <c r="G96" s="3">
-        <v>-1374300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-1395000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1411300</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-1432600</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-1358600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1464200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1361900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1472900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1573100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1668500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1564900</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1343800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1093100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1084100</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8049,8 +8285,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8141,8 +8380,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8233,280 +8475,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1150100</v>
+        <v>1275400</v>
       </c>
       <c r="E100" s="3">
-        <v>2065500</v>
+        <v>-1167400</v>
       </c>
       <c r="F100" s="3">
-        <v>-4752400</v>
+        <v>2096600</v>
       </c>
       <c r="G100" s="3">
-        <v>268900</v>
+        <v>-4824000</v>
       </c>
       <c r="H100" s="3">
-        <v>-123000</v>
+        <v>272900</v>
       </c>
       <c r="I100" s="3">
-        <v>687600</v>
+        <v>-124800</v>
       </c>
       <c r="J100" s="3">
+        <v>697900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-5668000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-258800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5545800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1634100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12979800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2024000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3087200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4957600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2601900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6920300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-102000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2742600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>115000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3031600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>138900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3545900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2541100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1473800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4333600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>616100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2694500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>74500</v>
+        <v>-96400</v>
       </c>
       <c r="E101" s="3">
-        <v>151500</v>
+        <v>75600</v>
       </c>
       <c r="F101" s="3">
-        <v>19500</v>
+        <v>153800</v>
       </c>
       <c r="G101" s="3">
-        <v>-140100</v>
+        <v>19800</v>
       </c>
       <c r="H101" s="3">
-        <v>100900</v>
+        <v>-142200</v>
       </c>
       <c r="I101" s="3">
-        <v>188700</v>
+        <v>102400</v>
       </c>
       <c r="J101" s="3">
+        <v>191500</v>
+      </c>
+      <c r="K101" s="3">
         <v>104400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>44900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>15600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>10600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>119900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-50400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-6100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-75300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>60900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-32900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-76500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>36000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-41700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>31800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-71700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>24900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>13800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>51100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>88300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2011300</v>
+        <v>1550400</v>
       </c>
       <c r="E102" s="3">
-        <v>1487300</v>
+        <v>-2041600</v>
       </c>
       <c r="F102" s="3">
-        <v>-185300</v>
+        <v>1509700</v>
       </c>
       <c r="G102" s="3">
-        <v>-843200</v>
+        <v>-188100</v>
       </c>
       <c r="H102" s="3">
-        <v>160000</v>
+        <v>-855900</v>
       </c>
       <c r="I102" s="3">
-        <v>598700</v>
+        <v>162400</v>
       </c>
       <c r="J102" s="3">
+        <v>607700</v>
+      </c>
+      <c r="K102" s="3">
         <v>54400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-541700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1687700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1496200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2957700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2540200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-515600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>332300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1392900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-478200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-859600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>690300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>362800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>176900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>859700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-889900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>124000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-669700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1540700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>776300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2309600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3101400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1283200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,218 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>22594400</v>
+        <v>23336200</v>
       </c>
       <c r="E8" s="3">
-        <v>21928600</v>
+        <v>21387600</v>
       </c>
       <c r="F8" s="3">
-        <v>20968600</v>
+        <v>20757300</v>
       </c>
       <c r="G8" s="3">
-        <v>24018700</v>
+        <v>19848600</v>
       </c>
       <c r="H8" s="3">
-        <v>22150500</v>
+        <v>22735800</v>
       </c>
       <c r="I8" s="3">
-        <v>21684600</v>
+        <v>20967300</v>
       </c>
       <c r="J8" s="3">
+        <v>20526400</v>
+      </c>
+      <c r="K8" s="3">
         <v>20684200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21468600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20854400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21594500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21260400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22730300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22185300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22940800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23597900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26753500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27085300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>27332100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26705400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29643300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28339000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>27316900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>25931300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27821100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27624000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>26057300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>25390800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>26880700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>25156800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>24903300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -940,29 +946,32 @@
       <c r="Z9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="3">
         <v>14315900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13646700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12122500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11756500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14418700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12033700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11724700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1035,29 +1044,32 @@
       <c r="Z10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB10" s="3">
         <v>13505200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13977300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13934700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13634400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>12462000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13123100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13178600</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1091,8 +1103,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1186,8 +1199,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,198 +1297,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>134100</v>
+        <v>387900</v>
       </c>
       <c r="E14" s="3">
-        <v>183300</v>
+        <v>126900</v>
       </c>
       <c r="F14" s="3">
-        <v>172300</v>
+        <v>173500</v>
       </c>
       <c r="G14" s="3">
-        <v>441900</v>
+        <v>163100</v>
       </c>
       <c r="H14" s="3">
-        <v>144400</v>
+        <v>418300</v>
       </c>
       <c r="I14" s="3">
-        <v>173400</v>
+        <v>136700</v>
       </c>
       <c r="J14" s="3">
+        <v>164100</v>
+      </c>
+      <c r="K14" s="3">
         <v>147400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>608900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>171800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>188300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>638700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>328000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>203600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>184200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>886600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>316400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>277500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>207800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1326000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>957400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>300900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>243400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>167300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2970900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>332400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>246800</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2743700</v>
+        <v>2722400</v>
       </c>
       <c r="E15" s="3">
-        <v>2687000</v>
+        <v>2597100</v>
       </c>
       <c r="F15" s="3">
-        <v>2670000</v>
+        <v>2543500</v>
       </c>
       <c r="G15" s="3">
-        <v>2736100</v>
+        <v>2527400</v>
       </c>
       <c r="H15" s="3">
-        <v>2664700</v>
+        <v>2590000</v>
       </c>
       <c r="I15" s="3">
-        <v>2639900</v>
+        <v>2522400</v>
       </c>
       <c r="J15" s="3">
+        <v>2498900</v>
+      </c>
+      <c r="K15" s="3">
         <v>2626200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2677800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2667600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2791000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2811400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2735500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2782000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2910000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3141000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3330600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3326500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3323100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3302300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3296200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3154600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3074900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2958700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3108500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>6102700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5974800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5995600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3364800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3683200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3208700</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1503,198 +1528,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18986900</v>
+        <v>20549900</v>
       </c>
       <c r="E17" s="3">
-        <v>18718300</v>
+        <v>17972700</v>
       </c>
       <c r="F17" s="3">
-        <v>17769500</v>
+        <v>17718500</v>
       </c>
       <c r="G17" s="3">
-        <v>21941700</v>
+        <v>16820400</v>
       </c>
       <c r="H17" s="3">
-        <v>18616700</v>
+        <v>20769700</v>
       </c>
       <c r="I17" s="3">
-        <v>18360600</v>
+        <v>17622400</v>
       </c>
       <c r="J17" s="3">
+        <v>17379900</v>
+      </c>
+      <c r="K17" s="3">
         <v>17291600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19948500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17210600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17823700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17686300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21531600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18566100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18960200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19353500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25769300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22825300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22942900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22077800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28041200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24030900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22360500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21047900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24898500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24267800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21413500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20647900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24918300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21679200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21008600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3607500</v>
+        <v>2786300</v>
       </c>
       <c r="E18" s="3">
-        <v>3210200</v>
+        <v>3414800</v>
       </c>
       <c r="F18" s="3">
-        <v>3199100</v>
+        <v>3038800</v>
       </c>
       <c r="G18" s="3">
-        <v>2077000</v>
+        <v>3028300</v>
       </c>
       <c r="H18" s="3">
-        <v>3533700</v>
+        <v>1966000</v>
       </c>
       <c r="I18" s="3">
-        <v>3324100</v>
+        <v>3345000</v>
       </c>
       <c r="J18" s="3">
+        <v>3146500</v>
+      </c>
+      <c r="K18" s="3">
         <v>3392600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1520100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3643800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3770800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3574100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1198700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3619200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3980600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4244400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>984300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4260000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4389200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4627600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1602100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4308200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4956500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4883400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2922500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3356200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4643800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4742900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1962400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3477700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3894700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1728,198 +1760,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-118000</v>
+        <v>-83600</v>
       </c>
       <c r="E20" s="3">
-        <v>-99300</v>
+        <v>-111700</v>
       </c>
       <c r="F20" s="3">
-        <v>693500</v>
+        <v>-94000</v>
       </c>
       <c r="G20" s="3">
-        <v>-137400</v>
+        <v>656400</v>
       </c>
       <c r="H20" s="3">
-        <v>-93200</v>
+        <v>-130100</v>
       </c>
       <c r="I20" s="3">
-        <v>4900</v>
+        <v>-88200</v>
       </c>
       <c r="J20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K20" s="3">
         <v>149500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>83900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>56800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-28800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>73600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-82200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-19800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-82500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-15500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-23300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>197800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-242800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-40300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>19900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>49300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1123500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>78400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>103800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>79200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>236000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>190600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6233200</v>
+        <v>5425100</v>
       </c>
       <c r="E21" s="3">
-        <v>5797900</v>
+        <v>5900300</v>
       </c>
       <c r="F21" s="3">
-        <v>6562600</v>
+        <v>5488200</v>
       </c>
       <c r="G21" s="3">
-        <v>4675700</v>
+        <v>6212100</v>
       </c>
       <c r="H21" s="3">
-        <v>6105200</v>
+        <v>4425900</v>
       </c>
       <c r="I21" s="3">
-        <v>5968800</v>
+        <v>5779100</v>
       </c>
       <c r="J21" s="3">
+        <v>5650000</v>
+      </c>
+      <c r="K21" s="3">
         <v>6168300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4281800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6368300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6533100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6459100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3852000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6373900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6870900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7377200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4232300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7571100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7689000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8127700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4655400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7422400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8051200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7891400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5939100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7548400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7734900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7838500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5406400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6963800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7254300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1974,8 +2013,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
@@ -1992,219 +2031,228 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
         <v>62500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>78700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>74500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>75300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>85100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>74400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3489600</v>
+        <v>2702700</v>
       </c>
       <c r="E23" s="3">
-        <v>3111000</v>
+        <v>3303200</v>
       </c>
       <c r="F23" s="3">
-        <v>3892600</v>
+        <v>2944800</v>
       </c>
       <c r="G23" s="3">
-        <v>1939600</v>
+        <v>3684700</v>
       </c>
       <c r="H23" s="3">
-        <v>3440500</v>
+        <v>1836000</v>
       </c>
       <c r="I23" s="3">
-        <v>3329000</v>
+        <v>3256700</v>
       </c>
       <c r="J23" s="3">
+        <v>3151200</v>
+      </c>
+      <c r="K23" s="3">
         <v>3542100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1604000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3700600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3742100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3647700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1116500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3591900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3960800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4236200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>901800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4244600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4365900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4825300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1359200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4267900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4976300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4932700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2841400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4401100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4647600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4771400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1956500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3639300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3998600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1081400</v>
+        <v>850200</v>
       </c>
       <c r="E24" s="3">
-        <v>1039700</v>
+        <v>1023700</v>
       </c>
       <c r="F24" s="3">
-        <v>1262900</v>
+        <v>984200</v>
       </c>
       <c r="G24" s="3">
-        <v>627600</v>
+        <v>1195400</v>
       </c>
       <c r="H24" s="3">
-        <v>1033900</v>
+        <v>594100</v>
       </c>
       <c r="I24" s="3">
-        <v>964900</v>
+        <v>978600</v>
       </c>
       <c r="J24" s="3">
+        <v>913300</v>
+      </c>
+      <c r="K24" s="3">
         <v>911600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>473200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1142600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1165700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1030900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>507000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1055300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1246800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1272500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>152100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1332200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1217500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1491500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>365800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1302600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1763500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1520700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>761900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1444900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1463800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1466700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>386100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1271900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1264100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2298,198 +2346,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2408100</v>
+        <v>1852500</v>
       </c>
       <c r="E26" s="3">
-        <v>2071200</v>
+        <v>2279500</v>
       </c>
       <c r="F26" s="3">
-        <v>2629700</v>
+        <v>1960600</v>
       </c>
       <c r="G26" s="3">
-        <v>1311900</v>
+        <v>2489300</v>
       </c>
       <c r="H26" s="3">
-        <v>2406600</v>
+        <v>1241900</v>
       </c>
       <c r="I26" s="3">
-        <v>2364100</v>
+        <v>2278100</v>
       </c>
       <c r="J26" s="3">
+        <v>2237800</v>
+      </c>
+      <c r="K26" s="3">
         <v>2630500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1130800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2558000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2576300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2616800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>609500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2536600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2714000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2963700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>749700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2912400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3148500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3333900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>993500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2965200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3212800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3412000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2079500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2956200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3183800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3304700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1570400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2367400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2734400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2293400</v>
+        <v>1712400</v>
       </c>
       <c r="E27" s="3">
-        <v>1988800</v>
+        <v>2170900</v>
       </c>
       <c r="F27" s="3">
-        <v>2532700</v>
+        <v>1882500</v>
       </c>
       <c r="G27" s="3">
-        <v>1217200</v>
+        <v>2397400</v>
       </c>
       <c r="H27" s="3">
-        <v>2264100</v>
+        <v>1152200</v>
       </c>
       <c r="I27" s="3">
-        <v>2211000</v>
+        <v>2143200</v>
       </c>
       <c r="J27" s="3">
+        <v>2092900</v>
+      </c>
+      <c r="K27" s="3">
         <v>2484200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2435500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2421400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2498900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>602700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2123200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2094500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2325600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>514400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2270700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2455000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2569700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>600000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2193900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2508100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2633800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1564900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2012000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2512900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2647500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1165500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1708600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2583,8 +2640,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2678,8 +2738,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2773,8 +2836,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2868,198 +2934,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>118000</v>
+        <v>83600</v>
       </c>
       <c r="E32" s="3">
-        <v>99300</v>
+        <v>111700</v>
       </c>
       <c r="F32" s="3">
-        <v>-693500</v>
+        <v>94000</v>
       </c>
       <c r="G32" s="3">
-        <v>137400</v>
+        <v>-656400</v>
       </c>
       <c r="H32" s="3">
-        <v>93200</v>
+        <v>130100</v>
       </c>
       <c r="I32" s="3">
-        <v>-4900</v>
+        <v>88200</v>
       </c>
       <c r="J32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-149500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-83900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-56800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>28800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-73600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>82200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>27200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>19800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>82500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>15500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>23300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-197800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>242800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>40300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-49300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>18700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1123500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-78400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-103800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-190600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2293400</v>
+        <v>1712400</v>
       </c>
       <c r="E33" s="3">
-        <v>1988800</v>
+        <v>2170900</v>
       </c>
       <c r="F33" s="3">
-        <v>2532700</v>
+        <v>1882500</v>
       </c>
       <c r="G33" s="3">
-        <v>1217200</v>
+        <v>2397400</v>
       </c>
       <c r="H33" s="3">
-        <v>2264100</v>
+        <v>1152200</v>
       </c>
       <c r="I33" s="3">
-        <v>2211000</v>
+        <v>2143200</v>
       </c>
       <c r="J33" s="3">
+        <v>2092900</v>
+      </c>
+      <c r="K33" s="3">
         <v>2484200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2435500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2421400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2498900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>602700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2123200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2094500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2325600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>514400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2270700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2455000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2569700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>600000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2193900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2508100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2633800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1564900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2012000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2512900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2647500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1165500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1708600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3153,203 +3228,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2293400</v>
+        <v>1712400</v>
       </c>
       <c r="E35" s="3">
-        <v>1988800</v>
+        <v>2170900</v>
       </c>
       <c r="F35" s="3">
-        <v>2532700</v>
+        <v>1882500</v>
       </c>
       <c r="G35" s="3">
-        <v>1217200</v>
+        <v>2397400</v>
       </c>
       <c r="H35" s="3">
-        <v>2264100</v>
+        <v>1152200</v>
       </c>
       <c r="I35" s="3">
-        <v>2211000</v>
+        <v>2143200</v>
       </c>
       <c r="J35" s="3">
+        <v>2092900</v>
+      </c>
+      <c r="K35" s="3">
         <v>2484200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2435500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2421400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2498900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>602700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2123200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2094500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2325600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>514400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2270700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2455000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2569700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>600000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2193900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2508100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2633800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1564900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2012000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2512900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2647500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1165500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1708600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3383,8 +3467,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3418,863 +3503,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6369600</v>
+        <v>6270700</v>
       </c>
       <c r="E41" s="3">
-        <v>4819200</v>
+        <v>6029400</v>
       </c>
       <c r="F41" s="3">
-        <v>6860700</v>
+        <v>4561800</v>
       </c>
       <c r="G41" s="3">
-        <v>5351000</v>
+        <v>6494300</v>
       </c>
       <c r="H41" s="3">
-        <v>5539100</v>
+        <v>5065200</v>
       </c>
       <c r="I41" s="3">
-        <v>6395000</v>
+        <v>5243300</v>
       </c>
       <c r="J41" s="3">
+        <v>6053500</v>
+      </c>
+      <c r="K41" s="3">
         <v>6232700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5541500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5677100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6526600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8373800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6634300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9916700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7839400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9148700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9105800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7975500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8527900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9356900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9092300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8575100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8264800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7245700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15144700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6929900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7599600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8690400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8206600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5897100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8998400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>729600</v>
+        <v>6203100</v>
       </c>
       <c r="E42" s="3">
-        <v>788800</v>
+        <v>690600</v>
       </c>
       <c r="F42" s="3">
-        <v>830200</v>
+        <v>746600</v>
       </c>
       <c r="G42" s="3">
-        <v>664900</v>
+        <v>785900</v>
       </c>
       <c r="H42" s="3">
-        <v>725800</v>
+        <v>629400</v>
       </c>
       <c r="I42" s="3">
-        <v>855400</v>
+        <v>687100</v>
       </c>
       <c r="J42" s="3">
+        <v>809700</v>
+      </c>
+      <c r="K42" s="3">
         <v>756300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>587200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>352000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>381600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>442400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>295900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4437100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5884200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>305000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>285300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1174300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1041400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>998300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1131600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1158300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1087400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1160200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1401100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>398600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1303600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>786800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>566300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>677900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>30136100</v>
+        <v>30732100</v>
       </c>
       <c r="E43" s="3">
-        <v>29084100</v>
+        <v>28526500</v>
       </c>
       <c r="F43" s="3">
-        <v>26128100</v>
+        <v>27530700</v>
       </c>
       <c r="G43" s="3">
-        <v>28216200</v>
+        <v>24732500</v>
       </c>
       <c r="H43" s="3">
-        <v>27592700</v>
+        <v>26709100</v>
       </c>
       <c r="I43" s="3">
-        <v>23993800</v>
+        <v>26118900</v>
       </c>
       <c r="J43" s="3">
+        <v>22712200</v>
+      </c>
+      <c r="K43" s="3">
         <v>22451800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23936900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24668900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21499000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22885100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>25060000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>27566200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>25444000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27582500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>30860000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>41217200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>37411000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>38645800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>42201700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>39166800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>36843100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>34757800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>68781300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>31235300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>29446200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26375400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>27995700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>29108000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>25063000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3773100</v>
+        <v>3344200</v>
       </c>
       <c r="E44" s="3">
-        <v>3783700</v>
+        <v>3571600</v>
       </c>
       <c r="F44" s="3">
-        <v>3765000</v>
+        <v>3581600</v>
       </c>
       <c r="G44" s="3">
-        <v>3487300</v>
+        <v>3563900</v>
       </c>
       <c r="H44" s="3">
-        <v>3341800</v>
+        <v>3301100</v>
       </c>
       <c r="I44" s="3">
-        <v>3183100</v>
+        <v>3163300</v>
       </c>
       <c r="J44" s="3">
+        <v>3013100</v>
+      </c>
+      <c r="K44" s="3">
         <v>2835300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2711500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2416000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2386300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2433500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2236400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2641700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2363200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2630700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2267100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2818000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2453800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2786700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3187000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4045200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3198000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3250000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6759800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4153400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3497200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3655500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3240900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3875200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3907300</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7687200</v>
+        <v>6557500</v>
       </c>
       <c r="E45" s="3">
-        <v>8203100</v>
+        <v>7276600</v>
       </c>
       <c r="F45" s="3">
-        <v>9380300</v>
+        <v>7764900</v>
       </c>
       <c r="G45" s="3">
-        <v>7134400</v>
+        <v>8879300</v>
       </c>
       <c r="H45" s="3">
-        <v>7792500</v>
+        <v>6753300</v>
       </c>
       <c r="I45" s="3">
-        <v>7830700</v>
+        <v>7376300</v>
       </c>
       <c r="J45" s="3">
+        <v>7412500</v>
+      </c>
+      <c r="K45" s="3">
         <v>7750300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5181000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4959400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4924400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5208500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3537400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4778900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4897300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17876500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16539700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5436400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5317700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6432000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7620800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7330500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7113200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5420500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9493000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5634700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5426600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6214100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7111600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7980800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7524600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>48695600</v>
+        <v>53107700</v>
       </c>
       <c r="E46" s="3">
-        <v>46678800</v>
+        <v>46094700</v>
       </c>
       <c r="F46" s="3">
-        <v>46964200</v>
+        <v>44185600</v>
       </c>
       <c r="G46" s="3">
-        <v>44853800</v>
+        <v>44455800</v>
       </c>
       <c r="H46" s="3">
-        <v>44992000</v>
+        <v>42458100</v>
       </c>
       <c r="I46" s="3">
-        <v>42258100</v>
+        <v>42588900</v>
       </c>
       <c r="J46" s="3">
+        <v>40001000</v>
+      </c>
+      <c r="K46" s="3">
         <v>40026400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37958200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38073500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35717900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39343300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37764000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49340600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>46428000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>57543400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>59057800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>58621500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>54751800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>58219800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>63233500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>60275800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>56506500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>51834100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>53057200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>48351800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>47273300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>45722100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47121200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>47539100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>46264000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>15281900</v>
+        <v>16987200</v>
       </c>
       <c r="E47" s="3">
-        <v>14825400</v>
+        <v>14465600</v>
       </c>
       <c r="F47" s="3">
-        <v>13429500</v>
+        <v>14033500</v>
       </c>
       <c r="G47" s="3">
-        <v>11376400</v>
+        <v>12712200</v>
       </c>
       <c r="H47" s="3">
-        <v>12871600</v>
+        <v>10768800</v>
       </c>
       <c r="I47" s="3">
-        <v>13366700</v>
+        <v>12184100</v>
       </c>
       <c r="J47" s="3">
+        <v>12652700</v>
+      </c>
+      <c r="K47" s="3">
         <v>13141700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12323600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13565400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14417400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14328900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13662100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13548000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13074400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12768700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9951600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14218700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13411900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13511100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13807300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13538500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13687300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14984100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>23831700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>9577600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>9086300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8923400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8691600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8571600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8135900</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>81320900</v>
+        <v>80656700</v>
       </c>
       <c r="E48" s="3">
-        <v>80847000</v>
+        <v>76977400</v>
       </c>
       <c r="F48" s="3">
-        <v>79432600</v>
+        <v>76528800</v>
       </c>
       <c r="G48" s="3">
-        <v>78711200</v>
+        <v>75189900</v>
       </c>
       <c r="H48" s="3">
-        <v>76419500</v>
+        <v>74507100</v>
       </c>
       <c r="I48" s="3">
-        <v>76637100</v>
+        <v>72337800</v>
       </c>
       <c r="J48" s="3">
+        <v>72543700</v>
+      </c>
+      <c r="K48" s="3">
         <v>76361000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>74753100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>77189000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>80463700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>82028500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>78731800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>79668500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>84222100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>91460600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>93742200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>95995400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>96175900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>95402300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>95907300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>92625800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>91769200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>89134300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>177505500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>87753100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>88621500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>87913000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>86207700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>84650400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>83893100</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>25946000</v>
+        <v>26857100</v>
       </c>
       <c r="E49" s="3">
-        <v>25759300</v>
+        <v>24560200</v>
       </c>
       <c r="F49" s="3">
-        <v>23748600</v>
+        <v>24383400</v>
       </c>
       <c r="G49" s="3">
-        <v>22958600</v>
+        <v>22480100</v>
       </c>
       <c r="H49" s="3">
-        <v>22484600</v>
+        <v>21732300</v>
       </c>
       <c r="I49" s="3">
-        <v>22510700</v>
+        <v>21283700</v>
       </c>
       <c r="J49" s="3">
+        <v>21308400</v>
+      </c>
+      <c r="K49" s="3">
         <v>22061500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21014500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20859600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20768100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21166700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20008300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19726800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20619900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22665300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>23565900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>24100000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23505500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23186600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24162400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23906500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23809200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23033500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>48621500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>26804000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>26981900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>26837400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>26415300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>25833000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>23543700</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4368,8 +4481,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4463,103 +4579,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12384900</v>
+        <v>11266300</v>
       </c>
       <c r="E52" s="3">
-        <v>12613000</v>
+        <v>11723400</v>
       </c>
       <c r="F52" s="3">
-        <v>12548300</v>
+        <v>11939300</v>
       </c>
       <c r="G52" s="3">
-        <v>12681600</v>
+        <v>11878100</v>
       </c>
       <c r="H52" s="3">
-        <v>12784200</v>
+        <v>12004200</v>
       </c>
       <c r="I52" s="3">
-        <v>12931000</v>
+        <v>12101400</v>
       </c>
       <c r="J52" s="3">
+        <v>12240300</v>
+      </c>
+      <c r="K52" s="3">
         <v>12887800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12396000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12062300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12440600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12789200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12659100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12624700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13703800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15336600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16437000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16063700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16481200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16408400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17145900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16387700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16004400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16148700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>30822500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22127200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22380200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>22405700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20054600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>19890900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4653,103 +4775,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>183629300</v>
+        <v>188874900</v>
       </c>
       <c r="E54" s="3">
-        <v>180723500</v>
+        <v>173821200</v>
       </c>
       <c r="F54" s="3">
-        <v>176123300</v>
+        <v>171070600</v>
       </c>
       <c r="G54" s="3">
-        <v>170581700</v>
+        <v>166716100</v>
       </c>
       <c r="H54" s="3">
-        <v>169551900</v>
+        <v>161470500</v>
       </c>
       <c r="I54" s="3">
-        <v>167703600</v>
+        <v>160495700</v>
       </c>
       <c r="J54" s="3">
+        <v>158746100</v>
+      </c>
+      <c r="K54" s="3">
         <v>164478300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>158445300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>161749700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>163807600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>169656600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>162825300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>174908600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>178048300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>199774600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>202754500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>208999200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>204326400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>206728300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>214256400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>206734400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>201776600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>195134800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>194734700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>194613800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>194343300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>191801600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>188490400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>186485000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>181367100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4783,8 +4911,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4818,578 +4947,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>17215400</v>
+        <v>18763100</v>
       </c>
       <c r="E57" s="3">
-        <v>16287200</v>
+        <v>16295900</v>
       </c>
       <c r="F57" s="3">
-        <v>16935100</v>
+        <v>15417300</v>
       </c>
       <c r="G57" s="3">
-        <v>7485000</v>
+        <v>16030500</v>
       </c>
       <c r="H57" s="3">
-        <v>16757100</v>
+        <v>7085200</v>
       </c>
       <c r="I57" s="3">
-        <v>14994100</v>
+        <v>15862000</v>
       </c>
       <c r="J57" s="3">
+        <v>14193200</v>
+      </c>
+      <c r="K57" s="3">
         <v>16106200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6541500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14575100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13308600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14666400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16709000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22680600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13558800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15530900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18877600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15531100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15365600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15442400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20108700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15250500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13794100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13731500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16378000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12341800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11209100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10462900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14307300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10823200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10149200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20043900</v>
+        <v>17650100</v>
       </c>
       <c r="E58" s="3">
-        <v>15880600</v>
+        <v>18973300</v>
       </c>
       <c r="F58" s="3">
-        <v>19048300</v>
+        <v>15032400</v>
       </c>
       <c r="G58" s="3">
-        <v>13786400</v>
+        <v>18030800</v>
       </c>
       <c r="H58" s="3">
-        <v>18857500</v>
+        <v>13050000</v>
       </c>
       <c r="I58" s="3">
-        <v>16708700</v>
+        <v>17850300</v>
       </c>
       <c r="J58" s="3">
+        <v>15816300</v>
+      </c>
+      <c r="K58" s="3">
         <v>15109700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12193000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14723800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16253200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28766600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>23840300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>38403300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>18080500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>21988600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>19458000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21904900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>16681400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>18869500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13565300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15598300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10476900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>14238400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15416900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>8838000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8994300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>9532100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8191800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>9374100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6176000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12483100</v>
+        <v>20022000</v>
       </c>
       <c r="E59" s="3">
-        <v>13593000</v>
+        <v>11816300</v>
       </c>
       <c r="F59" s="3">
-        <v>12427700</v>
+        <v>12866900</v>
       </c>
       <c r="G59" s="3">
-        <v>24830100</v>
+        <v>11763900</v>
       </c>
       <c r="H59" s="3">
-        <v>11206100</v>
+        <v>23503900</v>
       </c>
       <c r="I59" s="3">
-        <v>11945600</v>
+        <v>10607500</v>
       </c>
       <c r="J59" s="3">
+        <v>11307500</v>
+      </c>
+      <c r="K59" s="3">
         <v>11274200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22822800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10907200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11452200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10987400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12102100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10978900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12298300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17491000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19877400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13620000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14530600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14313800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16567700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14876600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15946100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14009300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>19934300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14207200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14711400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15808300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14146400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14897400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13836100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>49742400</v>
+        <v>56435200</v>
       </c>
       <c r="E60" s="3">
-        <v>45760800</v>
+        <v>47085500</v>
       </c>
       <c r="F60" s="3">
-        <v>48411000</v>
+        <v>43316600</v>
       </c>
       <c r="G60" s="3">
-        <v>46101500</v>
+        <v>45825300</v>
       </c>
       <c r="H60" s="3">
-        <v>46820700</v>
+        <v>43639100</v>
       </c>
       <c r="I60" s="3">
-        <v>43648300</v>
+        <v>44319900</v>
       </c>
       <c r="J60" s="3">
+        <v>41317000</v>
+      </c>
+      <c r="K60" s="3">
         <v>42490100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41557400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40206000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41014000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>54420400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>52651500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>72062700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>43937600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>55010500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>58213100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>51055900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>46577600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>48625600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>50241800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>45725300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>40217100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>41979300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>41786800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>35387100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>34914900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35803300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>36645500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>35094700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>30161200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51825400</v>
+        <v>50705300</v>
       </c>
       <c r="E61" s="3">
-        <v>52164300</v>
+        <v>49057300</v>
       </c>
       <c r="F61" s="3">
-        <v>48398800</v>
+        <v>49378100</v>
       </c>
       <c r="G61" s="3">
-        <v>47888200</v>
+        <v>45813700</v>
       </c>
       <c r="H61" s="3">
-        <v>45468300</v>
+        <v>45330400</v>
       </c>
       <c r="I61" s="3">
-        <v>46340900</v>
+        <v>43039700</v>
       </c>
       <c r="J61" s="3">
+        <v>43865800</v>
+      </c>
+      <c r="K61" s="3">
         <v>44393900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42318000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45383600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43143200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>36398100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>35517800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25696600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19853800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23192800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22413700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29780700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29372500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29574300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>27844600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27448700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>27278100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>25389200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28423700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28726400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28965100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>29015900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28331200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>29049600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>30307400</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13848400</v>
+        <v>12236700</v>
       </c>
       <c r="E62" s="3">
-        <v>13914500</v>
+        <v>13108700</v>
       </c>
       <c r="F62" s="3">
-        <v>13346600</v>
+        <v>13171300</v>
       </c>
       <c r="G62" s="3">
-        <v>13568700</v>
+        <v>12633700</v>
       </c>
       <c r="H62" s="3">
-        <v>15245700</v>
+        <v>12844000</v>
       </c>
       <c r="I62" s="3">
-        <v>15068900</v>
+        <v>14431400</v>
       </c>
       <c r="J62" s="3">
+        <v>14264100</v>
+      </c>
+      <c r="K62" s="3">
         <v>14949800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14689500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16384400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16927600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17223600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16496500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18169400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18967200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20608700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21142000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22174100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22177200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21883800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22726000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22825400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22206200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>21740200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>40355000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>21606000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21475400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21294000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>20989200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21797200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21685400</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5483,8 +5631,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5578,8 +5729,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5673,103 +5827,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>121391100</v>
+        <v>126069200</v>
       </c>
       <c r="E66" s="3">
-        <v>117927600</v>
+        <v>114907300</v>
       </c>
       <c r="F66" s="3">
-        <v>115817300</v>
+        <v>111628800</v>
       </c>
       <c r="G66" s="3">
-        <v>112878100</v>
+        <v>109631200</v>
       </c>
       <c r="H66" s="3">
-        <v>112765900</v>
+        <v>106849000</v>
       </c>
       <c r="I66" s="3">
-        <v>110612500</v>
+        <v>106742800</v>
       </c>
       <c r="J66" s="3">
+        <v>104704400</v>
+      </c>
+      <c r="K66" s="3">
         <v>107091700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103449800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106805100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106011600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>112803600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>109205700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>120390100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102256800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>119437400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>122926200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>125660600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>121280500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>123114000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>125220500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>119475700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>114165700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>112192700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>112807400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>109849800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>108990500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>108974100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>108194900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>107689800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>103690600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5803,8 +5963,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5898,8 +6059,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5993,8 +6157,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6088,8 +6255,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6183,103 +6353,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>58843400</v>
+        <v>57918200</v>
       </c>
       <c r="E72" s="3">
-        <v>58038000</v>
+        <v>55700400</v>
       </c>
       <c r="F72" s="3">
-        <v>56051900</v>
+        <v>54938000</v>
       </c>
       <c r="G72" s="3">
-        <v>54931800</v>
+        <v>53058000</v>
       </c>
       <c r="H72" s="3">
-        <v>52969400</v>
+        <v>51997700</v>
       </c>
       <c r="I72" s="3">
-        <v>52360000</v>
+        <v>50140100</v>
       </c>
       <c r="J72" s="3">
+        <v>49563300</v>
+      </c>
+      <c r="K72" s="3">
         <v>50164300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>48431600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>47910400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>54408400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52990500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50112200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50282400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>53498600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>56283300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>57264500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>58586300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>58367600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>55697400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>57220900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>55878100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>54359500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>57216800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>55490700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>55074400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>54544700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>52229600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>49904000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>48738500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>48114000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6373,8 +6549,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6468,8 +6647,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6563,103 +6745,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>62238200</v>
+        <v>62805700</v>
       </c>
       <c r="E76" s="3">
-        <v>62795900</v>
+        <v>58913900</v>
       </c>
       <c r="F76" s="3">
-        <v>60306000</v>
+        <v>59441900</v>
       </c>
       <c r="G76" s="3">
-        <v>57703500</v>
+        <v>57084900</v>
       </c>
       <c r="H76" s="3">
-        <v>56786100</v>
+        <v>54621400</v>
       </c>
       <c r="I76" s="3">
-        <v>57091100</v>
+        <v>53753000</v>
       </c>
       <c r="J76" s="3">
+        <v>54041700</v>
+      </c>
+      <c r="K76" s="3">
         <v>57386700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>54995500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54944700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57796000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>56853100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53619600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>54518600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>75791500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>80337200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>79828300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>83338500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>83045900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>83614300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>89035800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>87258700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>87610900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>82942000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>81927300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>84764000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>85352800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>82827500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>80295500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>78795200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>77676600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6753,203 +6941,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2293400</v>
+        <v>1712400</v>
       </c>
       <c r="E81" s="3">
-        <v>1988800</v>
+        <v>2170900</v>
       </c>
       <c r="F81" s="3">
-        <v>2532700</v>
+        <v>1882500</v>
       </c>
       <c r="G81" s="3">
-        <v>1217200</v>
+        <v>2397400</v>
       </c>
       <c r="H81" s="3">
-        <v>2264100</v>
+        <v>1152200</v>
       </c>
       <c r="I81" s="3">
-        <v>2211000</v>
+        <v>2143200</v>
       </c>
       <c r="J81" s="3">
+        <v>2092900</v>
+      </c>
+      <c r="K81" s="3">
         <v>2484200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2435500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2421400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2498900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>602700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2123200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2094500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2325600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>514400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2270700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2455000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2569700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>600000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2193900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2508100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2633800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1564900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2012000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2512900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2647500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1165500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1708600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6983,103 +7180,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2743700</v>
+        <v>2722400</v>
       </c>
       <c r="E83" s="3">
-        <v>2687000</v>
+        <v>2597100</v>
       </c>
       <c r="F83" s="3">
-        <v>2670000</v>
+        <v>2543500</v>
       </c>
       <c r="G83" s="3">
-        <v>2736100</v>
+        <v>2527400</v>
       </c>
       <c r="H83" s="3">
-        <v>2664700</v>
+        <v>2590000</v>
       </c>
       <c r="I83" s="3">
-        <v>2639900</v>
+        <v>2522400</v>
       </c>
       <c r="J83" s="3">
+        <v>2498900</v>
+      </c>
+      <c r="K83" s="3">
         <v>2626200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2677800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2667600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2791000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2811400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2735500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2782000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2910000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3141000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3330600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3326500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3323100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3302300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3296200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3154600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3074900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2958700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3035200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3068600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3000700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3003800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3364800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3250100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3169000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7173,8 +7374,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7268,8 +7472,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7363,8 +7570,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7458,8 +7668,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7553,103 +7766,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4088800</v>
+        <v>6007400</v>
       </c>
       <c r="E89" s="3">
-        <v>3269100</v>
+        <v>3870400</v>
       </c>
       <c r="F89" s="3">
-        <v>2297500</v>
+        <v>3094500</v>
       </c>
       <c r="G89" s="3">
-        <v>7584200</v>
+        <v>2174800</v>
       </c>
       <c r="H89" s="3">
-        <v>2218600</v>
+        <v>7179100</v>
       </c>
       <c r="I89" s="3">
-        <v>2651700</v>
+        <v>2100100</v>
       </c>
       <c r="J89" s="3">
+        <v>2510100</v>
+      </c>
+      <c r="K89" s="3">
         <v>2784700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7526700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2660500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6647700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4170800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9295200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2983500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6301300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4112300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11279800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1644300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9735800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4350900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7673800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3773500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7209000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3926000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7650900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6131900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5252800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4754300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10658100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2885700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7551100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7683,103 +7902,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-638898000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-502925000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-404987000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-537194000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-537220000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-430425000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-357543000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-526691000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-463257000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400176000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-378841000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3790900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3311400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3036100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2832700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4693900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4336700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3957900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3333700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5192700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4354400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3592000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3450900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4247500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2610700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2900200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2538600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3781500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3982200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3701000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2945900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7873,8 +8096,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7968,103 +8194,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3717400</v>
+        <v>-2303000</v>
       </c>
       <c r="E94" s="3">
-        <v>-4218900</v>
+        <v>-3518800</v>
       </c>
       <c r="F94" s="3">
-        <v>-3038200</v>
+        <v>-3993500</v>
       </c>
       <c r="G94" s="3">
-        <v>-2968200</v>
+        <v>-2875900</v>
       </c>
       <c r="H94" s="3">
-        <v>-3205200</v>
+        <v>-2809700</v>
       </c>
       <c r="I94" s="3">
-        <v>-2466900</v>
+        <v>-3034000</v>
       </c>
       <c r="J94" s="3">
+        <v>-2335200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-3066500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1908500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2988300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2805200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4319400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>606900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2416900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2929600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4854000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4785300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3642300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3482200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4604300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3669900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3349400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4960500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4575200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2977700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3913400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5183400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4066000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6691400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3502400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8098,103 +8330,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1434300</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-1357700</v>
       </c>
       <c r="F96" s="3">
-        <v>-1379200</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-1305500</v>
       </c>
       <c r="H96" s="3">
-        <v>-1395000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-1320500</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1432600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1358600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-1464200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-1361900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-1472900</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1573100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1668500</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1564900</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1343800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1093100</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1084100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8288,8 +8524,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8383,8 +8622,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8478,289 +8720,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1275400</v>
+        <v>-3582600</v>
       </c>
       <c r="E100" s="3">
-        <v>-1167400</v>
+        <v>1207300</v>
       </c>
       <c r="F100" s="3">
-        <v>2096600</v>
+        <v>-1105100</v>
       </c>
       <c r="G100" s="3">
-        <v>-4824000</v>
+        <v>1984600</v>
       </c>
       <c r="H100" s="3">
-        <v>272900</v>
+        <v>-4566300</v>
       </c>
       <c r="I100" s="3">
-        <v>-124800</v>
+        <v>258400</v>
       </c>
       <c r="J100" s="3">
+        <v>-118200</v>
+      </c>
+      <c r="K100" s="3">
         <v>697900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5668000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-258800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5545800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1634100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12979800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2024000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3087200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4957600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2601900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6920300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-102000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2742600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>115000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3031600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>138900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3545900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2541100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1473800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4333600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>616100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2694500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-96400</v>
+        <v>119600</v>
       </c>
       <c r="E101" s="3">
-        <v>75600</v>
+        <v>-91200</v>
       </c>
       <c r="F101" s="3">
-        <v>153800</v>
+        <v>71600</v>
       </c>
       <c r="G101" s="3">
-        <v>19800</v>
+        <v>145600</v>
       </c>
       <c r="H101" s="3">
-        <v>-142200</v>
+        <v>18800</v>
       </c>
       <c r="I101" s="3">
-        <v>102400</v>
+        <v>-134600</v>
       </c>
       <c r="J101" s="3">
+        <v>97000</v>
+      </c>
+      <c r="K101" s="3">
         <v>191500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>104400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>44900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>15600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>10600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>119900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-50400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-16800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-75300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>60900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-32900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-76500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>36000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-41700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>31800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-71700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>24900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>13800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>51100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>88300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1550400</v>
+        <v>241300</v>
       </c>
       <c r="E102" s="3">
-        <v>-2041600</v>
+        <v>1467600</v>
       </c>
       <c r="F102" s="3">
-        <v>1509700</v>
+        <v>-1932500</v>
       </c>
       <c r="G102" s="3">
-        <v>-188100</v>
+        <v>1429000</v>
       </c>
       <c r="H102" s="3">
-        <v>-855900</v>
+        <v>-178100</v>
       </c>
       <c r="I102" s="3">
-        <v>162400</v>
+        <v>-810200</v>
       </c>
       <c r="J102" s="3">
+        <v>153700</v>
+      </c>
+      <c r="K102" s="3">
         <v>607700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>54400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-541700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1687700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1496200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2957700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2540200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-515600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>332300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1392900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-478200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-859600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>690300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>362800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>176900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>859700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-889900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>124000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-669700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1540700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>776300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2309600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3101400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1283200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,224 +656,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>23336200</v>
+        <v>23004200</v>
       </c>
       <c r="E8" s="3">
-        <v>21387600</v>
+        <v>25969800</v>
       </c>
       <c r="F8" s="3">
-        <v>20757300</v>
+        <v>23801200</v>
       </c>
       <c r="G8" s="3">
-        <v>19848600</v>
+        <v>23099800</v>
       </c>
       <c r="H8" s="3">
-        <v>22735800</v>
+        <v>22088600</v>
       </c>
       <c r="I8" s="3">
-        <v>20967300</v>
+        <v>25301600</v>
       </c>
       <c r="J8" s="3">
+        <v>23333600</v>
+      </c>
+      <c r="K8" s="3">
         <v>20526400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20684200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21468600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20854400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21594500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21260400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22730300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22185300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22940800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23597900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26753500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>27085300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>27332100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26705400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>29643300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28339000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27316900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>25931300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27821100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>27624000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>26057300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>25390800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>26880700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>25156800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>24903300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -949,29 +955,32 @@
       <c r="AA9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC9" s="3">
         <v>14315900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13646700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12122500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11756500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14418700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12033700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11724700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1047,29 +1056,32 @@
       <c r="AA10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC10" s="3">
         <v>13505200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13977300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13934700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13634400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>12462000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13123100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13178600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1104,8 +1116,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1202,8 +1215,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,204 +1316,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>387900</v>
+        <v>156100</v>
       </c>
       <c r="E14" s="3">
-        <v>126900</v>
+        <v>431700</v>
       </c>
       <c r="F14" s="3">
-        <v>173500</v>
+        <v>141200</v>
       </c>
       <c r="G14" s="3">
-        <v>163100</v>
+        <v>193100</v>
       </c>
       <c r="H14" s="3">
-        <v>418300</v>
+        <v>181500</v>
       </c>
       <c r="I14" s="3">
-        <v>136700</v>
+        <v>465500</v>
       </c>
       <c r="J14" s="3">
+        <v>152100</v>
+      </c>
+      <c r="K14" s="3">
         <v>164100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>147400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>608900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>171800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>188300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>638700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>328000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>203600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>184200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>886600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>316400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>277500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>207800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1326000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>957400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>300900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>243400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>167300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2970900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>332400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>246800</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2722400</v>
+        <v>2985200</v>
       </c>
       <c r="E15" s="3">
-        <v>2597100</v>
+        <v>3029600</v>
       </c>
       <c r="F15" s="3">
-        <v>2543500</v>
+        <v>2890200</v>
       </c>
       <c r="G15" s="3">
-        <v>2527400</v>
+        <v>2830500</v>
       </c>
       <c r="H15" s="3">
-        <v>2590000</v>
+        <v>2812600</v>
       </c>
       <c r="I15" s="3">
-        <v>2522400</v>
+        <v>2882200</v>
       </c>
       <c r="J15" s="3">
+        <v>2807100</v>
+      </c>
+      <c r="K15" s="3">
         <v>2498900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2626200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2677800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2667600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2791000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2811400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2735500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2782000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2910000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3141000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3330600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3326500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3323100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3302300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3296200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3154600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3074900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2958700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3108500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>6102700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5974800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5995600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3364800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3683200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3208700</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1529,204 +1554,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20549900</v>
+        <v>19909900</v>
       </c>
       <c r="E17" s="3">
-        <v>17972700</v>
+        <v>22869000</v>
       </c>
       <c r="F17" s="3">
-        <v>17718500</v>
+        <v>20001000</v>
       </c>
       <c r="G17" s="3">
-        <v>16820400</v>
+        <v>19718100</v>
       </c>
       <c r="H17" s="3">
-        <v>20769700</v>
+        <v>18718600</v>
       </c>
       <c r="I17" s="3">
-        <v>17622400</v>
+        <v>23113600</v>
       </c>
       <c r="J17" s="3">
+        <v>19611100</v>
+      </c>
+      <c r="K17" s="3">
         <v>17379900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17291600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19948500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17210600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17823700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17686300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21531600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18566100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18960200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19353500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25769300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22825300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22942900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22077800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28041200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24030900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22360500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21047900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24898500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24267800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21413500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>20647900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24918300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21679200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21008600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2786300</v>
+        <v>3094300</v>
       </c>
       <c r="E18" s="3">
-        <v>3414800</v>
+        <v>3100700</v>
       </c>
       <c r="F18" s="3">
-        <v>3038800</v>
+        <v>3800200</v>
       </c>
       <c r="G18" s="3">
-        <v>3028300</v>
+        <v>3381700</v>
       </c>
       <c r="H18" s="3">
-        <v>1966000</v>
+        <v>3370000</v>
       </c>
       <c r="I18" s="3">
-        <v>3345000</v>
+        <v>2187900</v>
       </c>
       <c r="J18" s="3">
+        <v>3722500</v>
+      </c>
+      <c r="K18" s="3">
         <v>3146500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3392600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1520100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3643800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3770800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3574100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1198700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3619200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3980600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4244400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>984300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4260000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4389200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4627600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1602100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4308200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4956500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4883400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2922500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3356200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4643800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4742900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1962400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3477700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3894700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1761,204 +1793,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-83600</v>
+        <v>-45600</v>
       </c>
       <c r="E20" s="3">
-        <v>-111700</v>
+        <v>-93100</v>
       </c>
       <c r="F20" s="3">
-        <v>-94000</v>
+        <v>-124300</v>
       </c>
       <c r="G20" s="3">
-        <v>656400</v>
+        <v>-104600</v>
       </c>
       <c r="H20" s="3">
-        <v>-130100</v>
+        <v>730500</v>
       </c>
       <c r="I20" s="3">
-        <v>-88200</v>
+        <v>-144800</v>
       </c>
       <c r="J20" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="K20" s="3">
         <v>4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>149500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>83900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>56800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-28800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>73600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-82200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-27200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-19800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-82500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-15500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-23300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>197800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-242800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-40300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>19900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>49300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1123500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>78400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>103800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>79200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>236000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>190600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5425100</v>
+        <v>6033900</v>
       </c>
       <c r="E21" s="3">
-        <v>5900300</v>
+        <v>6037300</v>
       </c>
       <c r="F21" s="3">
-        <v>5488200</v>
+        <v>6566100</v>
       </c>
       <c r="G21" s="3">
-        <v>6212100</v>
+        <v>6107600</v>
       </c>
       <c r="H21" s="3">
-        <v>4425900</v>
+        <v>6913100</v>
       </c>
       <c r="I21" s="3">
-        <v>5779100</v>
+        <v>4925400</v>
       </c>
       <c r="J21" s="3">
+        <v>6431300</v>
+      </c>
+      <c r="K21" s="3">
         <v>5650000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6168300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4281800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6368300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6533100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6459100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3852000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6373900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6870900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7377200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4232300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7571100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7689000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8127700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4655400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7422400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8051200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7891400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5939100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7548400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7734900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7838500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5406400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6963800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7254300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2016,8 +2055,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
@@ -2034,225 +2073,234 @@
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>62500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>78700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>74500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>75300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>85100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>74400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2702700</v>
+        <v>3048700</v>
       </c>
       <c r="E23" s="3">
-        <v>3303200</v>
+        <v>3007700</v>
       </c>
       <c r="F23" s="3">
-        <v>2944800</v>
+        <v>3675900</v>
       </c>
       <c r="G23" s="3">
-        <v>3684700</v>
+        <v>3277100</v>
       </c>
       <c r="H23" s="3">
-        <v>1836000</v>
+        <v>4100500</v>
       </c>
       <c r="I23" s="3">
-        <v>3256700</v>
+        <v>2043200</v>
       </c>
       <c r="J23" s="3">
+        <v>3624300</v>
+      </c>
+      <c r="K23" s="3">
         <v>3151200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3542100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1604000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3700600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3742100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3647700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1116500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3591900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3960800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4236200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>901800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4244600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4365900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4825300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1359200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4267900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4976300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4932700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2841400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4401100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4647600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4771400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1956500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3639300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3998600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>850200</v>
+        <v>998300</v>
       </c>
       <c r="E24" s="3">
-        <v>1023700</v>
+        <v>946100</v>
       </c>
       <c r="F24" s="3">
-        <v>984200</v>
+        <v>1139200</v>
       </c>
       <c r="G24" s="3">
-        <v>1195400</v>
+        <v>1095300</v>
       </c>
       <c r="H24" s="3">
-        <v>594100</v>
+        <v>1330300</v>
       </c>
       <c r="I24" s="3">
-        <v>978600</v>
+        <v>661100</v>
       </c>
       <c r="J24" s="3">
+        <v>1089100</v>
+      </c>
+      <c r="K24" s="3">
         <v>913300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>911600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>473200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1142600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1165700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1030900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>507000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1055300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1246800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1272500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>152100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1332200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1217500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1491500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>365800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1302600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1763500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1520700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>761900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1444900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1463800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1466700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>386100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1271900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1264100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,204 +2397,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1852500</v>
+        <v>2050300</v>
       </c>
       <c r="E26" s="3">
-        <v>2279500</v>
+        <v>2061500</v>
       </c>
       <c r="F26" s="3">
-        <v>1960600</v>
+        <v>2536800</v>
       </c>
       <c r="G26" s="3">
-        <v>2489300</v>
+        <v>2181900</v>
       </c>
       <c r="H26" s="3">
-        <v>1241900</v>
+        <v>2770200</v>
       </c>
       <c r="I26" s="3">
-        <v>2278100</v>
+        <v>1382000</v>
       </c>
       <c r="J26" s="3">
+        <v>2535200</v>
+      </c>
+      <c r="K26" s="3">
         <v>2237800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2630500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1130800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2558000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2576300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2616800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>609500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2536600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2714000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2963700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>749700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2912400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3148500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3333900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>993500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2965200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3212800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3412000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2079500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2956200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3183800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3304700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1570400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2367400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2734400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1712400</v>
+        <v>1946400</v>
       </c>
       <c r="E27" s="3">
-        <v>2170900</v>
+        <v>1905700</v>
       </c>
       <c r="F27" s="3">
-        <v>1882500</v>
+        <v>2415900</v>
       </c>
       <c r="G27" s="3">
-        <v>2397400</v>
+        <v>2095000</v>
       </c>
       <c r="H27" s="3">
-        <v>1152200</v>
+        <v>2668000</v>
       </c>
       <c r="I27" s="3">
-        <v>2143200</v>
+        <v>1282200</v>
       </c>
       <c r="J27" s="3">
+        <v>2385000</v>
+      </c>
+      <c r="K27" s="3">
         <v>2092900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2484200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1000900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2435500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2421400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2498900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>602700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2123200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2094500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2325600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>514400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2270700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2455000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2569700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>600000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2193900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2508100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2633800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1564900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2012000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2512900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2647500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1165500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1708600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2643,8 +2700,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2741,8 +2801,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2839,8 +2902,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2937,204 +3003,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>83600</v>
+        <v>45600</v>
       </c>
       <c r="E32" s="3">
-        <v>111700</v>
+        <v>93100</v>
       </c>
       <c r="F32" s="3">
-        <v>94000</v>
+        <v>124300</v>
       </c>
       <c r="G32" s="3">
-        <v>-656400</v>
+        <v>104600</v>
       </c>
       <c r="H32" s="3">
-        <v>130100</v>
+        <v>-730500</v>
       </c>
       <c r="I32" s="3">
-        <v>88200</v>
+        <v>144800</v>
       </c>
       <c r="J32" s="3">
+        <v>98200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-149500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-83900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-56800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>28800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-73600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>82200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>27200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>19800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>82500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>15500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>23300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-197800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>242800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>40300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-49300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>18700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1123500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-78400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-103800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-190600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1712400</v>
+        <v>1946400</v>
       </c>
       <c r="E33" s="3">
-        <v>2170900</v>
+        <v>1905700</v>
       </c>
       <c r="F33" s="3">
-        <v>1882500</v>
+        <v>2415900</v>
       </c>
       <c r="G33" s="3">
-        <v>2397400</v>
+        <v>2095000</v>
       </c>
       <c r="H33" s="3">
-        <v>1152200</v>
+        <v>2668000</v>
       </c>
       <c r="I33" s="3">
-        <v>2143200</v>
+        <v>1282200</v>
       </c>
       <c r="J33" s="3">
+        <v>2385000</v>
+      </c>
+      <c r="K33" s="3">
         <v>2092900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2484200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1000900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2435500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2421400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2498900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>602700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2123200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2094500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2325600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>514400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2270700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2455000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2569700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>600000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2193900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2508100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2633800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1564900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2012000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2512900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2647500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1165500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1708600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3231,209 +3306,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1712400</v>
+        <v>1946400</v>
       </c>
       <c r="E35" s="3">
-        <v>2170900</v>
+        <v>1905700</v>
       </c>
       <c r="F35" s="3">
-        <v>1882500</v>
+        <v>2415900</v>
       </c>
       <c r="G35" s="3">
-        <v>2397400</v>
+        <v>2095000</v>
       </c>
       <c r="H35" s="3">
-        <v>1152200</v>
+        <v>2668000</v>
       </c>
       <c r="I35" s="3">
-        <v>2143200</v>
+        <v>1282200</v>
       </c>
       <c r="J35" s="3">
+        <v>2385000</v>
+      </c>
+      <c r="K35" s="3">
         <v>2092900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2484200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1000900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2435500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2421400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2498900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>602700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2123200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2094500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2325600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>514400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2270700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2455000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2569700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>600000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2193900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2508100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2633800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1564900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2012000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2512900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2647500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1165500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1708600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3468,8 +3552,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3504,890 +3589,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6270700</v>
+        <v>7911200</v>
       </c>
       <c r="E41" s="3">
-        <v>6029400</v>
+        <v>6978400</v>
       </c>
       <c r="F41" s="3">
-        <v>4561800</v>
+        <v>6709800</v>
       </c>
       <c r="G41" s="3">
-        <v>6494300</v>
+        <v>5076600</v>
       </c>
       <c r="H41" s="3">
-        <v>5065200</v>
+        <v>7227200</v>
       </c>
       <c r="I41" s="3">
-        <v>5243300</v>
+        <v>5636800</v>
       </c>
       <c r="J41" s="3">
+        <v>5835000</v>
+      </c>
+      <c r="K41" s="3">
         <v>6053500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6232700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5541500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5677100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6526600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8373800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6634300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9916700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7839400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9148700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9105800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7975500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8527900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9356900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9092300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8575100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8264800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7245700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>15144700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6929900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7599600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8690400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8206600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5897100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8998400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6203100</v>
+        <v>7291800</v>
       </c>
       <c r="E42" s="3">
-        <v>690600</v>
+        <v>6903200</v>
       </c>
       <c r="F42" s="3">
-        <v>746600</v>
+        <v>768500</v>
       </c>
       <c r="G42" s="3">
-        <v>785900</v>
+        <v>830900</v>
       </c>
       <c r="H42" s="3">
-        <v>629400</v>
+        <v>874500</v>
       </c>
       <c r="I42" s="3">
-        <v>687100</v>
+        <v>700400</v>
       </c>
       <c r="J42" s="3">
+        <v>764600</v>
+      </c>
+      <c r="K42" s="3">
         <v>809700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>756300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>587200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>352000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>381600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>442400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>295900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4437100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5884200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>305000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>285300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1174300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1041400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>998300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1131600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1158300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1087400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1160200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1401100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>398600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1303600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>786800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>566300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>677900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>30732100</v>
+        <v>31666300</v>
       </c>
       <c r="E43" s="3">
-        <v>28526500</v>
+        <v>34200400</v>
       </c>
       <c r="F43" s="3">
-        <v>27530700</v>
+        <v>31745700</v>
       </c>
       <c r="G43" s="3">
-        <v>24732500</v>
+        <v>30637600</v>
       </c>
       <c r="H43" s="3">
-        <v>26709100</v>
+        <v>27523600</v>
       </c>
       <c r="I43" s="3">
-        <v>26118900</v>
+        <v>29723300</v>
       </c>
       <c r="J43" s="3">
+        <v>29066500</v>
+      </c>
+      <c r="K43" s="3">
         <v>22712200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22451800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23936900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24668900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21499000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22885100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25060000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27566200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>25444000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27582500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>30860000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>41217200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>37411000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>38645800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>42201700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>39166800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>36843100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>34757800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>68781300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>31235300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>29446200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>26375400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>27995700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>29108000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>25063000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3344200</v>
+        <v>3836800</v>
       </c>
       <c r="E44" s="3">
-        <v>3571600</v>
+        <v>3721600</v>
       </c>
       <c r="F44" s="3">
-        <v>3581600</v>
+        <v>3974600</v>
       </c>
       <c r="G44" s="3">
-        <v>3563900</v>
+        <v>3985800</v>
       </c>
       <c r="H44" s="3">
-        <v>3301100</v>
+        <v>3966100</v>
       </c>
       <c r="I44" s="3">
-        <v>3163300</v>
+        <v>3673600</v>
       </c>
       <c r="J44" s="3">
+        <v>3520300</v>
+      </c>
+      <c r="K44" s="3">
         <v>3013100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2835300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2711500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2416000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2386300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2433500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2236400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2641700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2363200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2630700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2267100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2818000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2453800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2786700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3187000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4045200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3198000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3250000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6759800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4153400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3497200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3655500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3240900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3875200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3907300</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6557500</v>
+        <v>8584100</v>
       </c>
       <c r="E45" s="3">
-        <v>7276600</v>
+        <v>7297500</v>
       </c>
       <c r="F45" s="3">
-        <v>7764900</v>
+        <v>8097800</v>
       </c>
       <c r="G45" s="3">
-        <v>8879300</v>
+        <v>8641200</v>
       </c>
       <c r="H45" s="3">
-        <v>6753300</v>
+        <v>9881300</v>
       </c>
       <c r="I45" s="3">
-        <v>7376300</v>
+        <v>7515400</v>
       </c>
       <c r="J45" s="3">
+        <v>8208700</v>
+      </c>
+      <c r="K45" s="3">
         <v>7412500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7750300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5181000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4959400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4924400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5208500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3537400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4778900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4897300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17876500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16539700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5436400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5317700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6432000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7620800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7330500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7113200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5420500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9493000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5634700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5426600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6214100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7111600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7980800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7524600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>53107700</v>
+        <v>59290100</v>
       </c>
       <c r="E46" s="3">
-        <v>46094700</v>
+        <v>59101000</v>
       </c>
       <c r="F46" s="3">
-        <v>44185600</v>
+        <v>51296600</v>
       </c>
       <c r="G46" s="3">
-        <v>44455800</v>
+        <v>49172000</v>
       </c>
       <c r="H46" s="3">
-        <v>42458100</v>
+        <v>49472700</v>
       </c>
       <c r="I46" s="3">
-        <v>42588900</v>
+        <v>47249600</v>
       </c>
       <c r="J46" s="3">
+        <v>47395100</v>
+      </c>
+      <c r="K46" s="3">
         <v>40001000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40026400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37958200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38073500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35717900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39343300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37764000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>49340600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>46428000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>57543400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>59057800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>58621500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>54751800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>58219800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>63233500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>60275800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>56506500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>51834100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>53057200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>48351800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>47273300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>45722100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>47121200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>47539100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>46264000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>16987200</v>
+        <v>19426200</v>
       </c>
       <c r="E47" s="3">
-        <v>14465600</v>
+        <v>18904300</v>
       </c>
       <c r="F47" s="3">
-        <v>14033500</v>
+        <v>16098100</v>
       </c>
       <c r="G47" s="3">
-        <v>12712200</v>
+        <v>15617300</v>
       </c>
       <c r="H47" s="3">
-        <v>10768800</v>
+        <v>14146800</v>
       </c>
       <c r="I47" s="3">
-        <v>12184100</v>
+        <v>11984100</v>
       </c>
       <c r="J47" s="3">
+        <v>13559100</v>
+      </c>
+      <c r="K47" s="3">
         <v>12652700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13141700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12323600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13565400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14417400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14328900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13662100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13548000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13074400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12768700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9951600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14218700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13411900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13511100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13807300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13538500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13687300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14984100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>23831700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>9577600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9086300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8923400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8691600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8571600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8135900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>80656700</v>
+        <v>90730800</v>
       </c>
       <c r="E48" s="3">
-        <v>76977400</v>
+        <v>89759000</v>
       </c>
       <c r="F48" s="3">
-        <v>76528800</v>
+        <v>85664500</v>
       </c>
       <c r="G48" s="3">
-        <v>75189900</v>
+        <v>85165300</v>
       </c>
       <c r="H48" s="3">
-        <v>74507100</v>
+        <v>83675300</v>
       </c>
       <c r="I48" s="3">
-        <v>72337800</v>
+        <v>82915400</v>
       </c>
       <c r="J48" s="3">
+        <v>80501300</v>
+      </c>
+      <c r="K48" s="3">
         <v>72543700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>76361000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>74753100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>77189000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>80463700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>82028500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>78731800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>79668500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>84222100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>91460600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>93742200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>95995400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>96175900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>95402300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>95907300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>92625800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>91769200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>89134300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>177505500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>87753100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>88621500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>87913000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>86207700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>84650400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>83893100</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>26857100</v>
+        <v>30736500</v>
       </c>
       <c r="E49" s="3">
-        <v>24560200</v>
+        <v>29888000</v>
       </c>
       <c r="F49" s="3">
-        <v>24383400</v>
+        <v>27331900</v>
       </c>
       <c r="G49" s="3">
-        <v>22480100</v>
+        <v>27135200</v>
       </c>
       <c r="H49" s="3">
-        <v>21732300</v>
+        <v>25017100</v>
       </c>
       <c r="I49" s="3">
-        <v>21283700</v>
+        <v>24184900</v>
       </c>
       <c r="J49" s="3">
+        <v>23685600</v>
+      </c>
+      <c r="K49" s="3">
         <v>21308400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22061500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21014500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20859600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20768100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>21166700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20008300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19726800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20619900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22665300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23565900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>24100000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23505500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23186600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24162400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23906500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23809200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23033500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>48621500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>26804000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>26981900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>26837400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>26415300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>25833000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>23543700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4484,8 +4597,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4582,106 +4698,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11266300</v>
+        <v>12741100</v>
       </c>
       <c r="E52" s="3">
-        <v>11723400</v>
+        <v>12537700</v>
       </c>
       <c r="F52" s="3">
-        <v>11939300</v>
+        <v>13046500</v>
       </c>
       <c r="G52" s="3">
-        <v>11878100</v>
+        <v>13286700</v>
       </c>
       <c r="H52" s="3">
-        <v>12004200</v>
+        <v>13218600</v>
       </c>
       <c r="I52" s="3">
-        <v>12101400</v>
+        <v>13358900</v>
       </c>
       <c r="J52" s="3">
+        <v>13467100</v>
+      </c>
+      <c r="K52" s="3">
         <v>12240300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12887800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12396000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12062300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12440600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12789200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12659100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12624700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13703800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15336600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16437000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16063700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16481200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16408400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17145900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16387700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16004400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16148700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>30822500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22127200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>22380200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>22405700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20054600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>19890900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4778,106 +4900,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>188874900</v>
+        <v>212924800</v>
       </c>
       <c r="E54" s="3">
-        <v>173821200</v>
+        <v>210190000</v>
       </c>
       <c r="F54" s="3">
-        <v>171070600</v>
+        <v>193437400</v>
       </c>
       <c r="G54" s="3">
-        <v>166716100</v>
+        <v>190376400</v>
       </c>
       <c r="H54" s="3">
-        <v>161470500</v>
+        <v>185530500</v>
       </c>
       <c r="I54" s="3">
-        <v>160495700</v>
+        <v>179692800</v>
       </c>
       <c r="J54" s="3">
+        <v>178608100</v>
+      </c>
+      <c r="K54" s="3">
         <v>158746100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>164478300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>158445300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>161749700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>163807600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>169656600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>162825300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>174908600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>178048300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>199774600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>202754500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>208999200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>204326400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>206728300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>214256400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>206734400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>201776600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>195134800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>194734700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>194613800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>194343300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>191801600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>188490400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>186485000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>181367100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4912,8 +5040,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4948,596 +5077,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>18763100</v>
+        <v>17720800</v>
       </c>
       <c r="E57" s="3">
-        <v>16295900</v>
+        <v>8022700</v>
       </c>
       <c r="F57" s="3">
-        <v>15417300</v>
+        <v>18134900</v>
       </c>
       <c r="G57" s="3">
-        <v>16030500</v>
+        <v>17157100</v>
       </c>
       <c r="H57" s="3">
-        <v>7085200</v>
+        <v>17839600</v>
       </c>
       <c r="I57" s="3">
-        <v>15862000</v>
+        <v>7884800</v>
       </c>
       <c r="J57" s="3">
+        <v>17652100</v>
+      </c>
+      <c r="K57" s="3">
         <v>14193200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16106200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6541500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14575100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13308600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14666400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16709000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22680600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13558800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15530900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>18877600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15531100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15365600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15442400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20108700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15250500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13794100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13731500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>16378000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12341800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11209100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10462900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>14307300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10823200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10149200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17650100</v>
+        <v>26072500</v>
       </c>
       <c r="E58" s="3">
-        <v>18973300</v>
+        <v>19642000</v>
       </c>
       <c r="F58" s="3">
-        <v>15032400</v>
+        <v>21114500</v>
       </c>
       <c r="G58" s="3">
-        <v>18030800</v>
+        <v>16728900</v>
       </c>
       <c r="H58" s="3">
-        <v>13050000</v>
+        <v>20065700</v>
       </c>
       <c r="I58" s="3">
-        <v>17850300</v>
+        <v>14522700</v>
       </c>
       <c r="J58" s="3">
+        <v>19864800</v>
+      </c>
+      <c r="K58" s="3">
         <v>15816300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15109700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12193000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14723800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16253200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>28766600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23840300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>38403300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18080500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21988600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>19458000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21904900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>16681400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>18869500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>13565300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>15598300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10476900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>14238400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15416900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8838000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8994300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9532100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8191800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9374100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>6176000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20022000</v>
+        <v>19742800</v>
       </c>
       <c r="E59" s="3">
-        <v>11816300</v>
+        <v>35139500</v>
       </c>
       <c r="F59" s="3">
-        <v>12866900</v>
+        <v>13149800</v>
       </c>
       <c r="G59" s="3">
-        <v>11763900</v>
+        <v>14319000</v>
       </c>
       <c r="H59" s="3">
-        <v>23503900</v>
+        <v>13091400</v>
       </c>
       <c r="I59" s="3">
-        <v>10607500</v>
+        <v>26156400</v>
       </c>
       <c r="J59" s="3">
+        <v>11804600</v>
+      </c>
+      <c r="K59" s="3">
         <v>11307500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11274200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22822800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10907200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11452200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10987400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12102100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10978900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12298300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17491000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19877400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13620000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14530600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14313800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16567700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14876600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15946100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14009300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19934300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14207200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14711400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15808300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14146400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14897400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13836100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>56435200</v>
+        <v>63536100</v>
       </c>
       <c r="E60" s="3">
-        <v>47085500</v>
+        <v>62804100</v>
       </c>
       <c r="F60" s="3">
-        <v>43316600</v>
+        <v>52399200</v>
       </c>
       <c r="G60" s="3">
-        <v>45825300</v>
+        <v>48205000</v>
       </c>
       <c r="H60" s="3">
-        <v>43639100</v>
+        <v>50996800</v>
       </c>
       <c r="I60" s="3">
-        <v>44319900</v>
+        <v>48563900</v>
       </c>
       <c r="J60" s="3">
+        <v>49321500</v>
+      </c>
+      <c r="K60" s="3">
         <v>41317000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>42490100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41557400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40206000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41014000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>54420400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>52651500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>72062700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>43937600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>55010500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>58213100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>51055900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>46577600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>48625600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>50241800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>45725300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>40217100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>41979300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>41786800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>35387100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>34914900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>35803300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>36645500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>35094700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>30161200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>50705300</v>
+        <v>57036500</v>
       </c>
       <c r="E61" s="3">
-        <v>49057300</v>
+        <v>56427500</v>
       </c>
       <c r="F61" s="3">
-        <v>49378100</v>
+        <v>54593500</v>
       </c>
       <c r="G61" s="3">
-        <v>45813700</v>
+        <v>54950500</v>
       </c>
       <c r="H61" s="3">
-        <v>45330400</v>
+        <v>50983900</v>
       </c>
       <c r="I61" s="3">
-        <v>43039700</v>
+        <v>50446100</v>
       </c>
       <c r="J61" s="3">
+        <v>47896900</v>
+      </c>
+      <c r="K61" s="3">
         <v>43865800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44393900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42318000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45383600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43143200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>36398100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>35517800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25696600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19853800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23192800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>22413700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29780700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29372500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29574300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27844600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>27448700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>27278100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25389200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28423700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28726400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28965100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>29015900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28331200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>29049600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>30307400</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12236700</v>
+        <v>13765200</v>
       </c>
       <c r="E62" s="3">
-        <v>13108700</v>
+        <v>13617700</v>
       </c>
       <c r="F62" s="3">
-        <v>13171300</v>
+        <v>14588100</v>
       </c>
       <c r="G62" s="3">
-        <v>12633700</v>
+        <v>14657700</v>
       </c>
       <c r="H62" s="3">
-        <v>12844000</v>
+        <v>14059500</v>
       </c>
       <c r="I62" s="3">
-        <v>14431400</v>
+        <v>14293400</v>
       </c>
       <c r="J62" s="3">
+        <v>16060000</v>
+      </c>
+      <c r="K62" s="3">
         <v>14264100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14949800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14689500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16384400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16927600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17223600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16496500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18169400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18967200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20608700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21142000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22174100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22177200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21883800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22726000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22825400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>22206200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>21740200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>40355000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21606000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21475400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21294000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>20989200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21797200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21685400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5634,8 +5782,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5732,8 +5883,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5830,106 +5984,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>126069200</v>
+        <v>142151100</v>
       </c>
       <c r="E66" s="3">
-        <v>114907300</v>
+        <v>140296400</v>
       </c>
       <c r="F66" s="3">
-        <v>111628800</v>
+        <v>127874900</v>
       </c>
       <c r="G66" s="3">
-        <v>109631200</v>
+        <v>124226400</v>
       </c>
       <c r="H66" s="3">
-        <v>106849000</v>
+        <v>122003300</v>
       </c>
       <c r="I66" s="3">
-        <v>106742800</v>
+        <v>118907200</v>
       </c>
       <c r="J66" s="3">
+        <v>118789000</v>
+      </c>
+      <c r="K66" s="3">
         <v>104704400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>107091700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103449800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106805100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106011600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>112803600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>109205700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>120390100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102256800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>119437400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>122926200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>125660600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>121280500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>123114000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>125220500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>119475700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>114165700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>112192700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>112807400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>109849800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>108990500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>108974100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>108194900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>107689800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>103690600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5964,8 +6124,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6062,8 +6223,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6160,8 +6324,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6258,8 +6425,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6356,106 +6526,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>57918200</v>
+        <v>64837000</v>
       </c>
       <c r="E72" s="3">
-        <v>55700400</v>
+        <v>64454400</v>
       </c>
       <c r="F72" s="3">
-        <v>54938000</v>
+        <v>61986400</v>
       </c>
       <c r="G72" s="3">
-        <v>53058000</v>
+        <v>61138000</v>
       </c>
       <c r="H72" s="3">
-        <v>51997700</v>
+        <v>59045800</v>
       </c>
       <c r="I72" s="3">
-        <v>50140100</v>
+        <v>57865800</v>
       </c>
       <c r="J72" s="3">
+        <v>55798600</v>
+      </c>
+      <c r="K72" s="3">
         <v>49563300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50164300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>48431600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>47910400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>54408400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52990500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50112200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50282400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>53498600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>56283300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>57264500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>58586300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>58367600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>55697400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>57220900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>55878100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>54359500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>57216800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>55490700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>55074400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>54544700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>52229600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>49904000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>48738500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>48114000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6552,8 +6728,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6650,8 +6829,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6748,106 +6930,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>62805700</v>
+        <v>70773700</v>
       </c>
       <c r="E76" s="3">
-        <v>58913900</v>
+        <v>69893500</v>
       </c>
       <c r="F76" s="3">
-        <v>59441900</v>
+        <v>65562500</v>
       </c>
       <c r="G76" s="3">
-        <v>57084900</v>
+        <v>66150000</v>
       </c>
       <c r="H76" s="3">
-        <v>54621400</v>
+        <v>63527100</v>
       </c>
       <c r="I76" s="3">
-        <v>53753000</v>
+        <v>60785600</v>
       </c>
       <c r="J76" s="3">
+        <v>59819100</v>
+      </c>
+      <c r="K76" s="3">
         <v>54041700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>57386700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54995500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>54944700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>57796000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>56853100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53619600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>54518600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>75791500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>80337200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>79828300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>83338500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>83045900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>83614300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>89035800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>87258700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>87610900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>82942000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>81927300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>84764000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>85352800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>82827500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>80295500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>78795200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>77676600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6944,209 +7132,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1712400</v>
+        <v>1946400</v>
       </c>
       <c r="E81" s="3">
-        <v>2170900</v>
+        <v>1905700</v>
       </c>
       <c r="F81" s="3">
-        <v>1882500</v>
+        <v>2415900</v>
       </c>
       <c r="G81" s="3">
-        <v>2397400</v>
+        <v>2095000</v>
       </c>
       <c r="H81" s="3">
-        <v>1152200</v>
+        <v>2668000</v>
       </c>
       <c r="I81" s="3">
-        <v>2143200</v>
+        <v>1282200</v>
       </c>
       <c r="J81" s="3">
+        <v>2385000</v>
+      </c>
+      <c r="K81" s="3">
         <v>2092900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2484200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1000900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2435500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2421400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2498900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>602700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2123200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2094500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2325600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>514400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2270700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2455000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2569700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>600000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2193900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2508100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2633800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1564900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2012000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2512900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2647500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1165500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1708600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7181,106 +7378,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2722400</v>
+        <v>2985200</v>
       </c>
       <c r="E83" s="3">
-        <v>2597100</v>
+        <v>3029600</v>
       </c>
       <c r="F83" s="3">
-        <v>2543500</v>
+        <v>2890200</v>
       </c>
       <c r="G83" s="3">
-        <v>2527400</v>
+        <v>2830500</v>
       </c>
       <c r="H83" s="3">
-        <v>2590000</v>
+        <v>2812600</v>
       </c>
       <c r="I83" s="3">
-        <v>2522400</v>
+        <v>2882200</v>
       </c>
       <c r="J83" s="3">
+        <v>2807100</v>
+      </c>
+      <c r="K83" s="3">
         <v>2498900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2626200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2677800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2667600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2791000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2811400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2735500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2782000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2910000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3141000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3330600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3326500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3323100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3302300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3296200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3154600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3074900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2958700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3035200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3068600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3000700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3003800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3364800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3250100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3169000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7377,8 +7578,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7475,8 +7679,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7573,8 +7780,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7671,8 +7881,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7769,106 +7982,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>6007400</v>
+        <v>1385500</v>
       </c>
       <c r="E89" s="3">
-        <v>3870400</v>
+        <v>6685400</v>
       </c>
       <c r="F89" s="3">
-        <v>3094500</v>
+        <v>4307200</v>
       </c>
       <c r="G89" s="3">
-        <v>2174800</v>
+        <v>3443700</v>
       </c>
       <c r="H89" s="3">
-        <v>7179100</v>
+        <v>2420200</v>
       </c>
       <c r="I89" s="3">
-        <v>2100100</v>
+        <v>7989300</v>
       </c>
       <c r="J89" s="3">
+        <v>2337100</v>
+      </c>
+      <c r="K89" s="3">
         <v>2510100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2784700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7526700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2660500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6647700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4170800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9295200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2983500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6301300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4112300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11279800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1644300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9735800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4350900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7673800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3773500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7209000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3926000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7650900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6131900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5252800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4754300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>10658100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2885700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>7551100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7903,106 +8122,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-566096000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-638898000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-502925000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-404987000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-537194000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-537220000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-430425000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-357543000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-526691000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-463257000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400176000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-378841000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3790900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3311400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3036100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2832700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4693900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4336700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3957900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3333700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5192700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4354400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3592000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3450900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4247500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2610700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2900200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2538600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3781500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3982200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3701000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2945900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8099,8 +8322,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8197,106 +8423,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2303000</v>
+        <v>-4159300</v>
       </c>
       <c r="E94" s="3">
-        <v>-3518800</v>
+        <v>-2562900</v>
       </c>
       <c r="F94" s="3">
-        <v>-3993500</v>
+        <v>-3916000</v>
       </c>
       <c r="G94" s="3">
-        <v>-2875900</v>
+        <v>-4444200</v>
       </c>
       <c r="H94" s="3">
-        <v>-2809700</v>
+        <v>-3200500</v>
       </c>
       <c r="I94" s="3">
-        <v>-3034000</v>
+        <v>-3126700</v>
       </c>
       <c r="J94" s="3">
+        <v>-3376400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2335200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3066500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1908500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2988300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2805200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4319400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>606900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2416900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2929600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4854000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4785300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3642300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3482200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4604300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3669900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3349400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4960500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4575200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2977700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3913400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5183400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4066000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6691400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3502400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8331,106 +8563,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-1552600</v>
       </c>
       <c r="E96" s="3">
-        <v>-1357700</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-1510900</v>
       </c>
       <c r="G96" s="3">
-        <v>-1305500</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-1452900</v>
       </c>
       <c r="I96" s="3">
-        <v>-1320500</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-1469500</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-1432600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1358600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1464200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1361900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1472900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1573100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1668500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1564900</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1343800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1093100</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1084100</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8527,8 +8763,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8625,8 +8864,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8723,298 +8965,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3582600</v>
+        <v>3585800</v>
       </c>
       <c r="E100" s="3">
-        <v>1207300</v>
+        <v>-3987000</v>
       </c>
       <c r="F100" s="3">
-        <v>-1105100</v>
+        <v>1343600</v>
       </c>
       <c r="G100" s="3">
-        <v>1984600</v>
+        <v>-1229800</v>
       </c>
       <c r="H100" s="3">
-        <v>-4566300</v>
+        <v>2208600</v>
       </c>
       <c r="I100" s="3">
-        <v>258400</v>
+        <v>-5081600</v>
       </c>
       <c r="J100" s="3">
+        <v>287500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-118200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>697900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5668000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-258800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5545800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1634100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12979800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2024000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3087200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4957600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2601900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6920300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-102000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2742600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>115000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3031600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>138900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3545900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2541100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1473800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4333600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>616100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2694500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>119600</v>
+        <v>120800</v>
       </c>
       <c r="E101" s="3">
-        <v>-91200</v>
+        <v>133100</v>
       </c>
       <c r="F101" s="3">
-        <v>71600</v>
+        <v>-101500</v>
       </c>
       <c r="G101" s="3">
-        <v>145600</v>
+        <v>79700</v>
       </c>
       <c r="H101" s="3">
-        <v>18800</v>
+        <v>162000</v>
       </c>
       <c r="I101" s="3">
-        <v>-134600</v>
+        <v>20900</v>
       </c>
       <c r="J101" s="3">
+        <v>-149800</v>
+      </c>
+      <c r="K101" s="3">
         <v>97000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>191500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>104400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>44900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>15600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>119900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-50400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-16800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-75300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>60900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-32900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-76500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>36000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-41700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>31800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-71700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>24900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>13800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>51100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>88300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>241300</v>
+        <v>932800</v>
       </c>
       <c r="E102" s="3">
-        <v>1467600</v>
+        <v>268600</v>
       </c>
       <c r="F102" s="3">
-        <v>-1932500</v>
+        <v>1633300</v>
       </c>
       <c r="G102" s="3">
-        <v>1429000</v>
+        <v>-2150600</v>
       </c>
       <c r="H102" s="3">
-        <v>-178100</v>
+        <v>1590300</v>
       </c>
       <c r="I102" s="3">
-        <v>-810200</v>
+        <v>-198200</v>
       </c>
       <c r="J102" s="3">
+        <v>-901600</v>
+      </c>
+      <c r="K102" s="3">
         <v>153700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>607700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>54400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-541700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1687700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1496200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2957700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2540200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-515600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>332300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1392900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-478200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-859600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>690300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>362800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>176900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>859700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-889900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>124000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-669700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1540700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>776300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2309600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3101400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1283200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,230 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>23004200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>25969800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>23801200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>23099800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>22088600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>25301600</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>23333600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20526400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20684200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21468600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20854400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21594500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21260400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22730300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22185300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22940800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>23597900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26753500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>27085300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27332100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26705400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>29643300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>28339000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27316900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>25931300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>27821100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27624000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>26057300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>25390800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>26880700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>25156800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>24903300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -958,29 +965,32 @@
       <c r="AB9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD9" s="3">
         <v>14315900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13646700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12122500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11756500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14418700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12033700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>11724700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,29 +1069,32 @@
       <c r="AB10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="3">
         <v>13505200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13977300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13934700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13634400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>12462000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13123100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13178600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1117,8 +1130,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1218,8 +1232,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,210 +1336,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>156100</v>
-      </c>
-      <c r="E14" s="3">
-        <v>431700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>141200</v>
-      </c>
-      <c r="G14" s="3">
-        <v>193100</v>
-      </c>
-      <c r="H14" s="3">
-        <v>181500</v>
-      </c>
-      <c r="I14" s="3">
-        <v>465500</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>152100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>164100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>147400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>608900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>171800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>188300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>638700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>328000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>203600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>184200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>886600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>316400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>277500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>207800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1326000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>957400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>300900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>243400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>167300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2970900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>332400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>246800</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>2985200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3029600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2890200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2830500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2812600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2882200</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3">
         <v>2807100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2498900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2626200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2677800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2667600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2791000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2811400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2735500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2782000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2910000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3141000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3330600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3326500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3323100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3302300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3296200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3154600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3074900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2958700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3108500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>6102700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5974800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5995600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3364800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3683200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3208700</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1555,210 +1581,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>19909900</v>
-      </c>
-      <c r="E17" s="3">
-        <v>22869000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>20001000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>19718100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>18718600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>23113600</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>19611100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17379900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17291600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19948500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17210600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17823700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17686300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21531600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18566100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18960200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19353500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25769300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22825300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22942900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22077800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28041200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24030900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22360500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21047900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24898500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24267800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21413500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>20647900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>24918300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21679200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21008600</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>3094300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>3100700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3800200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>3381700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>3370000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2187900</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>3722500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3146500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3392600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1520100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3643800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3770800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3574100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1198700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3619200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3980600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4244400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>984300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4260000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4389200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4627600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1602100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4308200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4956500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4883400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2922500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3356200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4643800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4742900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1962400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3477700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3894700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1794,233 +1827,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-45600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-93100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-124300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-104600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>730500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-144800</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-98200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>149500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>83900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>56800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-28800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>73600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-82200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-27200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-19800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-82500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-15500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-23300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>197800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-242800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-40300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>19900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>49300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1123500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>78400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>103800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>79200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>236000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>190600</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>6033900</v>
-      </c>
-      <c r="E21" s="3">
-        <v>6037300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>6566100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>6107600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>6913100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>4925400</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>6431300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5650000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6168300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4281800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6368300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6533100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6459100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3852000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6373900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6870900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7377200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4232300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7571100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7689000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8127700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4655400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7422400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8051200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7891400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5939100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7548400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7734900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7838500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5406400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6963800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7254300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2058,8 +2098,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -2076,231 +2116,240 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>62500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>78700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>74500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>75300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>85100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>74400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>3048700</v>
-      </c>
-      <c r="E23" s="3">
-        <v>3007700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>3675900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>3277100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>4100500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2043200</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>3624300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3151200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3542100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1604000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3700600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3742100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3647700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1116500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3591900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3960800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4236200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>901800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4244600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4365900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4825300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1359200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4267900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4976300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4932700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2841400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4401100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4647600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4771400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1956500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3639300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3998600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>998300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>946100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1139200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1095300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1330300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>661100</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>1089100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>913300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>911600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>473200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1142600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1165700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1030900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>507000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1055300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1246800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1272500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>152100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1332200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1217500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1491500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>365800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1302600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1763500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1520700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>761900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1444900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1463800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1466700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>386100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1271900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1264100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,210 +2449,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>2050300</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2061500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>2536800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>2181900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>2770200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1382000</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>2535200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2237800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2630500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1130800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2558000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2576300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2616800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>609500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2536600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2714000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2963700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>749700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2912400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3148500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3333900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>993500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2965200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3212800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3412000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2079500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2956200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3183800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3304700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1570400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2367400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2734400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>1946400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1905700</v>
-      </c>
-      <c r="F27" s="3">
-        <v>2415900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2095000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2668000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1282200</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>2385000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2092900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2484200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1000900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2435500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2421400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2498900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>602700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2123200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2094500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2325600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>514400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2270700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2455000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2569700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>600000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2193900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2508100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2633800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1564900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2012000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2512900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2647500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1165500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1708600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2703,31 +2761,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2804,8 +2865,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2905,8 +2969,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3006,210 +3073,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>45600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>93100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>124300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>104600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-730500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>144800</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>98200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-149500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-83900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-56800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>28800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-73600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>82200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>27200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>19800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>82500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>15500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>23300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-197800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>242800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>40300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-49300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>18700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1123500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-78400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-103800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-190600</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>1946400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1905700</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2415900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>2095000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>2668000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1282200</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>2385000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2092900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2484200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1000900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2435500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2421400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2498900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>602700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2123200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2094500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2325600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>514400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2270700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2455000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2569700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>600000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2193900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2508100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2633800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1564900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2012000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2512900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2647500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1165500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1708600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3309,215 +3385,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>1946400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1905700</v>
-      </c>
-      <c r="F35" s="3">
-        <v>2415900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>2095000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>2668000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1282200</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>2385000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2092900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2484200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1000900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2435500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2421400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2498900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>602700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2123200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2094500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2325600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>514400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2270700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2455000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2569700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>600000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2193900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2508100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2633800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1564900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2012000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2512900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2647500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1165500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1708600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3553,8 +3638,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3590,917 +3676,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7911200</v>
+        <v>8431000</v>
       </c>
       <c r="E41" s="3">
-        <v>6978400</v>
+        <v>6926600</v>
       </c>
       <c r="F41" s="3">
-        <v>6709800</v>
+        <v>6498100</v>
       </c>
       <c r="G41" s="3">
-        <v>5076600</v>
+        <v>6704300</v>
       </c>
       <c r="H41" s="3">
-        <v>7227200</v>
+        <v>4787100</v>
       </c>
       <c r="I41" s="3">
-        <v>5636800</v>
+        <v>7040200</v>
       </c>
       <c r="J41" s="3">
+        <v>5972300</v>
+      </c>
+      <c r="K41" s="3">
         <v>5835000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6053500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6232700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5541500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5677100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6526600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8373800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6634300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9916700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7839400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9148700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9105800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7975500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8527900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9356900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9092300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8575100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8264800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7245700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15144700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6929900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7599600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8690400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8206600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5897100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8998400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>7291800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>6903200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>768500</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>830900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>874500</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>700400</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>764600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>809700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>756300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>587200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>352000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>381600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>442400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>295900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4437100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5884200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>305000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>285300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1174300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1041400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>998300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1131600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1158300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1087400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1160200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1401100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>398600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1303600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>786800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>566300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>677900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>31666300</v>
+        <v>30111900</v>
       </c>
       <c r="E43" s="3">
-        <v>34200400</v>
+        <v>27725200</v>
       </c>
       <c r="F43" s="3">
-        <v>31745700</v>
+        <v>31846600</v>
       </c>
       <c r="G43" s="3">
-        <v>30637600</v>
+        <v>31719400</v>
       </c>
       <c r="H43" s="3">
-        <v>27523600</v>
+        <v>28890500</v>
       </c>
       <c r="I43" s="3">
-        <v>29723300</v>
+        <v>26811700</v>
       </c>
       <c r="J43" s="3">
+        <v>31492100</v>
+      </c>
+      <c r="K43" s="3">
         <v>29066500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22712200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22451800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23936900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24668900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21499000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22885100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>25060000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27566200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>25444000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27582500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>30860000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>41217200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>37411000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>38645800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>42201700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>39166800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>36843100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>34757800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>68781300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>31235300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>29446200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>26375400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>27995700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>29108000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>25063000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3836800</v>
+        <v>4056600</v>
       </c>
       <c r="E44" s="3">
-        <v>3721600</v>
+        <v>3359200</v>
       </c>
       <c r="F44" s="3">
-        <v>3974600</v>
+        <v>3465400</v>
       </c>
       <c r="G44" s="3">
-        <v>3985800</v>
+        <v>3971300</v>
       </c>
       <c r="H44" s="3">
-        <v>3966100</v>
+        <v>3758500</v>
       </c>
       <c r="I44" s="3">
-        <v>3673600</v>
+        <v>3863500</v>
       </c>
       <c r="J44" s="3">
+        <v>3892200</v>
+      </c>
+      <c r="K44" s="3">
         <v>3520300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3013100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2835300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2711500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2416000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2386300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2433500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2236400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2641700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2363200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2630700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2267100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2818000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2453800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2786700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3187000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4045200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3198000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3250000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6759800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4153400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3497200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3655500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3240900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3875200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3907300</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8584100</v>
+        <v>13064500</v>
       </c>
       <c r="E45" s="3">
-        <v>7297500</v>
+        <v>13900100</v>
       </c>
       <c r="F45" s="3">
-        <v>8097800</v>
+        <v>13223300</v>
       </c>
       <c r="G45" s="3">
-        <v>8641200</v>
+        <v>8859000</v>
       </c>
       <c r="H45" s="3">
-        <v>9881300</v>
+        <v>8932000</v>
       </c>
       <c r="I45" s="3">
-        <v>7515400</v>
+        <v>10477600</v>
       </c>
       <c r="J45" s="3">
+        <v>8704800</v>
+      </c>
+      <c r="K45" s="3">
         <v>8208700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7412500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7750300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5181000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4959400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4924400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5208500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3537400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4778900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4897300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17876500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16539700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5436400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5317700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6432000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7620800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7330500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7113200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5420500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9493000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5634700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5426600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6214100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7111600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7980800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7524600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>59290100</v>
+        <v>55664000</v>
       </c>
       <c r="E46" s="3">
-        <v>59101000</v>
+        <v>51911100</v>
       </c>
       <c r="F46" s="3">
-        <v>51296600</v>
+        <v>55033500</v>
       </c>
       <c r="G46" s="3">
-        <v>49172000</v>
+        <v>51254000</v>
       </c>
       <c r="H46" s="3">
-        <v>49472700</v>
+        <v>46368100</v>
       </c>
       <c r="I46" s="3">
-        <v>47249600</v>
+        <v>48193000</v>
       </c>
       <c r="J46" s="3">
+        <v>50061400</v>
+      </c>
+      <c r="K46" s="3">
         <v>47395100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40001000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40026400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37958200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>38073500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35717900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39343300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37764000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>49340600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>46428000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>57543400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>59057800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>58621500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>54751800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>58219800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>63233500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>60275800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>56506500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>51834100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>53057200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>48351800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47273300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>45722100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>47121200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>47539100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>46264000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>19426200</v>
+        <v>34125400</v>
       </c>
       <c r="E47" s="3">
-        <v>18904300</v>
+        <v>2640900</v>
       </c>
       <c r="F47" s="3">
-        <v>16098100</v>
+        <v>33184900</v>
       </c>
       <c r="G47" s="3">
-        <v>15617300</v>
+        <v>32103300</v>
       </c>
       <c r="H47" s="3">
-        <v>14146800</v>
+        <v>29805800</v>
       </c>
       <c r="I47" s="3">
-        <v>11984100</v>
+        <v>29115400</v>
       </c>
       <c r="J47" s="3">
+        <v>29126000</v>
+      </c>
+      <c r="K47" s="3">
         <v>13559100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12652700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13141700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12323600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13565400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14417400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14328900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13662100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13548000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13074400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12768700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9951600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14218700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13411900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13511100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13807300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13538500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13687300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>14984100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>23831700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9577600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>9086300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8923400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8691600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8571600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8135900</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>90730800</v>
+        <v>78980000</v>
       </c>
       <c r="E48" s="3">
-        <v>89759000</v>
+        <v>71244700</v>
       </c>
       <c r="F48" s="3">
-        <v>85664500</v>
+        <v>74952200</v>
       </c>
       <c r="G48" s="3">
-        <v>85165300</v>
+        <v>76618500</v>
       </c>
       <c r="H48" s="3">
-        <v>83675300</v>
+        <v>71768300</v>
       </c>
       <c r="I48" s="3">
-        <v>82915400</v>
+        <v>72809000</v>
       </c>
       <c r="J48" s="3">
+        <v>78502400</v>
+      </c>
+      <c r="K48" s="3">
         <v>80501300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72543700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>76361000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>74753100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>77189000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>80463700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>82028500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>78731800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>79668500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>84222100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>91460600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>93742200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>95995400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>96175900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>95402300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>95907300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>92625800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>91769200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>89134300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>177505500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>87753100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>88621500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>87913000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>86207700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>84650400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>83893100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>30736500</v>
+        <v>28930900</v>
       </c>
       <c r="E49" s="3">
-        <v>29888000</v>
+        <v>26911100</v>
       </c>
       <c r="F49" s="3">
-        <v>27331900</v>
+        <v>27831000</v>
       </c>
       <c r="G49" s="3">
-        <v>27135200</v>
+        <v>27309200</v>
       </c>
       <c r="H49" s="3">
-        <v>25017100</v>
+        <v>25587900</v>
       </c>
       <c r="I49" s="3">
-        <v>24184900</v>
+        <v>24370000</v>
       </c>
       <c r="J49" s="3">
+        <v>25624200</v>
+      </c>
+      <c r="K49" s="3">
         <v>23685600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21308400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22061500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21014500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20859600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20768100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>21166700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20008300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19726800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>20619900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22665300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23565900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>24100000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23505500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23186600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24162400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23906500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23809200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23033500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>48621500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>26804000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>26981900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>26837400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>26415300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>25833000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>23543700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4600,8 +4714,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4701,109 +4818,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>12741100</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
-        <v>12537700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>13046500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>13286700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>13218600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>13358900</v>
-      </c>
-      <c r="J52" s="3">
+        <v>29217200</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>13467100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12240300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12887800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12396000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12062300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12440600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12789200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12659100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12624700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13703800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15336600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16437000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16063700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16481200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16408400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17145900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16387700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16004400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16148700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>30822500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>22127200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>22380200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>22405700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>20054600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>19890900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4903,109 +5026,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>212924800</v>
+        <v>202742900</v>
       </c>
       <c r="E54" s="3">
-        <v>210190000</v>
+        <v>186424800</v>
       </c>
       <c r="F54" s="3">
-        <v>193437400</v>
+        <v>195723900</v>
       </c>
       <c r="G54" s="3">
-        <v>190376400</v>
+        <v>193277000</v>
       </c>
       <c r="H54" s="3">
-        <v>185530500</v>
+        <v>179520700</v>
       </c>
       <c r="I54" s="3">
-        <v>179692800</v>
+        <v>180731400</v>
       </c>
       <c r="J54" s="3">
+        <v>190386600</v>
+      </c>
+      <c r="K54" s="3">
         <v>178608100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>158746100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>164478300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>158445300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>161749700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>163807600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>169656600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>162825300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>174908600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>178048300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>199774600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>202754500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>208999200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>204326400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>206728300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>214256400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>206734400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>201776600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>195134800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>194734700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>194613800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>194343300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>191801600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>188490400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>186485000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>181367100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5041,8 +5170,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5078,614 +5208,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>17720800</v>
+        <v>16650400</v>
       </c>
       <c r="E57" s="3">
-        <v>8022700</v>
+        <v>15515300</v>
       </c>
       <c r="F57" s="3">
-        <v>18134900</v>
+        <v>19443500</v>
       </c>
       <c r="G57" s="3">
-        <v>17157100</v>
+        <v>18119800</v>
       </c>
       <c r="H57" s="3">
-        <v>17839600</v>
+        <v>16178800</v>
       </c>
       <c r="I57" s="3">
-        <v>7884800</v>
+        <v>17378200</v>
       </c>
       <c r="J57" s="3">
+        <v>21117900</v>
+      </c>
+      <c r="K57" s="3">
         <v>17652100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14193200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16106200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6541500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14575100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13308600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14666400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16709000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>22680600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13558800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15530900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18877600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15531100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15365600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15442400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>20108700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15250500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13794100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13731500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>16378000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12341800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11209100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10462900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>14307300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10823200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10149200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>26072500</v>
+        <v>20167500</v>
       </c>
       <c r="E58" s="3">
-        <v>19642000</v>
+        <v>22827600</v>
       </c>
       <c r="F58" s="3">
-        <v>21114500</v>
+        <v>18290100</v>
       </c>
       <c r="G58" s="3">
-        <v>16728900</v>
+        <v>21097000</v>
       </c>
       <c r="H58" s="3">
-        <v>20065700</v>
+        <v>15775000</v>
       </c>
       <c r="I58" s="3">
-        <v>14522700</v>
+        <v>19546600</v>
       </c>
       <c r="J58" s="3">
+        <v>15387000</v>
+      </c>
+      <c r="K58" s="3">
         <v>19864800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15816300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15109700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12193000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14723800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16253200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>28766600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>23840300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>38403300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>18080500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21988600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>19458000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21904900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>16681400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>18869500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>13565300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15598300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10476900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>14238400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15416900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8838000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8994300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>9532100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8191800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>9374100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>6176000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19742800</v>
+        <v>15708300</v>
       </c>
       <c r="E59" s="3">
-        <v>35139500</v>
+        <v>14249300</v>
       </c>
       <c r="F59" s="3">
-        <v>13149800</v>
+        <v>16675800</v>
       </c>
       <c r="G59" s="3">
-        <v>14319000</v>
+        <v>9909300</v>
       </c>
       <c r="H59" s="3">
-        <v>13091400</v>
+        <v>9730100</v>
       </c>
       <c r="I59" s="3">
-        <v>26156400</v>
+        <v>9622800</v>
       </c>
       <c r="J59" s="3">
+        <v>10659600</v>
+      </c>
+      <c r="K59" s="3">
         <v>11804600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11307500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11274200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22822800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10907200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11452200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10987400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12102100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10978900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12298300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17491000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19877400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13620000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14530600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14313800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16567700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14876600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15946100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14009300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>19934300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14207200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14711400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15808300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14146400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14897400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13836100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>63536100</v>
+        <v>56071700</v>
       </c>
       <c r="E60" s="3">
-        <v>62804100</v>
+        <v>55628600</v>
       </c>
       <c r="F60" s="3">
-        <v>52399200</v>
+        <v>58475200</v>
       </c>
       <c r="G60" s="3">
-        <v>48205000</v>
+        <v>52321600</v>
       </c>
       <c r="H60" s="3">
-        <v>50996800</v>
+        <v>45028600</v>
       </c>
       <c r="I60" s="3">
-        <v>48563900</v>
+        <v>49650300</v>
       </c>
       <c r="J60" s="3">
+        <v>51431000</v>
+      </c>
+      <c r="K60" s="3">
         <v>49321500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41317000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>42490100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41557400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40206000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41014000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>54420400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>52651500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72062700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43937600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>55010500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>58213100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>51055900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>46577600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>48625600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>50241800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>45725300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>40217100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>41979300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>41786800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35387100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>34914900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>35803300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>36645500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>35094700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>30161200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>57036500</v>
+        <v>56105200</v>
       </c>
       <c r="E61" s="3">
-        <v>56427500</v>
+        <v>49937900</v>
       </c>
       <c r="F61" s="3">
-        <v>54593500</v>
+        <v>52544000</v>
       </c>
       <c r="G61" s="3">
-        <v>54950500</v>
+        <v>54548300</v>
       </c>
       <c r="H61" s="3">
-        <v>50983900</v>
+        <v>51817100</v>
       </c>
       <c r="I61" s="3">
-        <v>50446100</v>
+        <v>49665100</v>
       </c>
       <c r="J61" s="3">
+        <v>53448200</v>
+      </c>
+      <c r="K61" s="3">
         <v>47896900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>43865800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44393900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42318000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45383600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>43143200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36398100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>35517800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>25696600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19853800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23192800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22413700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29780700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29372500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29574300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>27844600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>27448700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>27278100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>25389200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28423700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28726400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28965100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>29015900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28331200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>29049600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>30307400</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13765200</v>
+        <v>3794900</v>
       </c>
       <c r="E62" s="3">
-        <v>13617700</v>
+        <v>3486600</v>
       </c>
       <c r="F62" s="3">
-        <v>14588100</v>
+        <v>3571700</v>
       </c>
       <c r="G62" s="3">
-        <v>14657700</v>
+        <v>3634500</v>
       </c>
       <c r="H62" s="3">
-        <v>14059500</v>
+        <v>3859600</v>
       </c>
       <c r="I62" s="3">
-        <v>14293400</v>
+        <v>3212500</v>
       </c>
       <c r="J62" s="3">
+        <v>3841200</v>
+      </c>
+      <c r="K62" s="3">
         <v>16060000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14264100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14949800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14689500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16384400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16927600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17223600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16496500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18169400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18967200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>20608700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21142000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22174100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22177200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21883800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22726000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>22825400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>22206200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>21740200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>40355000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21606000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21475400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21294000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>20989200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21797200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21685400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5785,8 +5934,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5886,8 +6038,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5987,109 +6142,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>142151100</v>
+        <v>125574900</v>
       </c>
       <c r="E66" s="3">
-        <v>140296400</v>
+        <v>117618600</v>
       </c>
       <c r="F66" s="3">
-        <v>127874900</v>
+        <v>123706100</v>
       </c>
       <c r="G66" s="3">
-        <v>124226400</v>
+        <v>121480000</v>
       </c>
       <c r="H66" s="3">
-        <v>122003300</v>
+        <v>111095300</v>
       </c>
       <c r="I66" s="3">
-        <v>118907200</v>
+        <v>113038600</v>
       </c>
       <c r="J66" s="3">
+        <v>120046200</v>
+      </c>
+      <c r="K66" s="3">
         <v>118789000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>104704400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>107091700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103449800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106805100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>106011600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>112803600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>109205700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>120390100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>102256800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>119437400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>122926200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>125660600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>121280500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>123114000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>125220500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>119475700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>114165700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>112192700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>112807400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>109849800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>108990500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>108974100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>108194900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>107689800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>103690600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6125,8 +6286,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6226,8 +6388,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6327,8 +6492,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6428,8 +6596,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6529,109 +6700,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>64837000</v>
+        <v>65935800</v>
       </c>
       <c r="E72" s="3">
-        <v>64454400</v>
+        <v>56767600</v>
       </c>
       <c r="F72" s="3">
-        <v>61986400</v>
+        <v>60018400</v>
       </c>
       <c r="G72" s="3">
-        <v>61138000</v>
+        <v>61935000</v>
       </c>
       <c r="H72" s="3">
-        <v>59045800</v>
+        <v>57651700</v>
       </c>
       <c r="I72" s="3">
-        <v>57865800</v>
+        <v>57518400</v>
       </c>
       <c r="J72" s="3">
+        <v>61309500</v>
+      </c>
+      <c r="K72" s="3">
         <v>55798600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49563300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50164300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48431600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>47910400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>54408400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52990500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50112200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>50282400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>53498600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>56283300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>57264500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>58586300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>58367600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>55697400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>57220900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>55878100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>54359500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>57216800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>55490700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>55074400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>54544700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>52229600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>49904000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>48738500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>48114000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6731,8 +6908,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6832,8 +7012,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6933,109 +7116,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>70773700</v>
+        <v>69737300</v>
       </c>
       <c r="E76" s="3">
-        <v>69893500</v>
+        <v>61965400</v>
       </c>
       <c r="F76" s="3">
-        <v>65562500</v>
+        <v>65083200</v>
       </c>
       <c r="G76" s="3">
-        <v>66150000</v>
+        <v>65508100</v>
       </c>
       <c r="H76" s="3">
-        <v>63527100</v>
+        <v>62378000</v>
       </c>
       <c r="I76" s="3">
-        <v>60785600</v>
+        <v>61883900</v>
       </c>
       <c r="J76" s="3">
+        <v>64403000</v>
+      </c>
+      <c r="K76" s="3">
         <v>59819100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>54041700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>57386700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>54995500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>54944700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>57796000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56853100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53619600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>54518600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75791500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>80337200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>79828300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>83338500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>83045900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>83614300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>89035800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>87258700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>87610900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>82942000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>81927300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>84764000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>85352800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>82827500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>80295500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>78795200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>77676600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7135,215 +7324,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>1946400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1905700</v>
-      </c>
-      <c r="F81" s="3">
-        <v>2415900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>2095000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>2668000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1282200</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>2385000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2092900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2484200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1000900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2435500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2421400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2498900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>602700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2123200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2094500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2325600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>514400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2270700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2455000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2569700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>600000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2193900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2508100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2633800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1564900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2012000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2512900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2647500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1165500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1708600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7379,109 +7577,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2985200</v>
+        <v>2669100</v>
       </c>
       <c r="E83" s="3">
-        <v>3029600</v>
+        <v>2739900</v>
       </c>
       <c r="F83" s="3">
-        <v>2890200</v>
+        <v>3053800</v>
       </c>
       <c r="G83" s="3">
-        <v>2830500</v>
+        <v>2998100</v>
       </c>
       <c r="H83" s="3">
-        <v>2812600</v>
+        <v>2707000</v>
       </c>
       <c r="I83" s="3">
-        <v>2882200</v>
+        <v>2867300</v>
       </c>
       <c r="J83" s="3">
+        <v>3321000</v>
+      </c>
+      <c r="K83" s="3">
         <v>2807100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2498900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2626200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2677800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2667600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2791000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2811400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2735500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2782000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2910000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3141000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3330600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3326500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3323100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3302300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3296200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3154600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3074900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2958700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3035200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3068600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3000700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3003800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3364800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3250100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3169000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7581,8 +7783,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7682,8 +7887,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7783,8 +7991,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7884,8 +8095,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7985,109 +8199,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1385500</v>
+        <v>6465200</v>
       </c>
       <c r="E89" s="3">
-        <v>6685400</v>
+        <v>1213000</v>
       </c>
       <c r="F89" s="3">
-        <v>4307200</v>
+        <v>6225300</v>
       </c>
       <c r="G89" s="3">
-        <v>3443700</v>
+        <v>4303600</v>
       </c>
       <c r="H89" s="3">
-        <v>2420200</v>
+        <v>3247400</v>
       </c>
       <c r="I89" s="3">
-        <v>7989300</v>
+        <v>2357600</v>
       </c>
       <c r="J89" s="3">
+        <v>8464800</v>
+      </c>
+      <c r="K89" s="3">
         <v>2337100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2510100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2784700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7526700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2660500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6647700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4170800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9295200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2983500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6301300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4112300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11279800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1644300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9735800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4350900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7673800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3773500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7209000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3926000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7650900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6131900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5252800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4754300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10658100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2885700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7551100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8123,109 +8343,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-566096000</v>
+        <v>-3060200</v>
       </c>
       <c r="E91" s="3">
-        <v>-638898000</v>
+        <v>-3519100</v>
       </c>
       <c r="F91" s="3">
-        <v>-502925000</v>
+        <v>-4224000</v>
       </c>
       <c r="G91" s="3">
-        <v>-404987000</v>
+        <v>-3567800</v>
       </c>
       <c r="H91" s="3">
-        <v>-537194000</v>
+        <v>-2711400</v>
       </c>
       <c r="I91" s="3">
-        <v>-537220000</v>
+        <v>-3715400</v>
       </c>
       <c r="J91" s="3">
+        <v>-4041300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-430425000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-357543000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-526691000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-463257000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400176000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-378841000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3790900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3311400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3036100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2832700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4693900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4336700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3957900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3333700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5192700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4354400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3592000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3450900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4247500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2610700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2900200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2538600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3781500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3982200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3701000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2945900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8325,8 +8549,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8426,109 +8653,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4159300</v>
+        <v>-2496900</v>
       </c>
       <c r="E94" s="3">
-        <v>-2562900</v>
+        <v>-3641700</v>
       </c>
       <c r="F94" s="3">
-        <v>-3916000</v>
+        <v>-2386500</v>
       </c>
       <c r="G94" s="3">
-        <v>-4444200</v>
+        <v>-3912700</v>
       </c>
       <c r="H94" s="3">
-        <v>-3200500</v>
+        <v>-4190800</v>
       </c>
       <c r="I94" s="3">
-        <v>-3126700</v>
+        <v>-3117700</v>
       </c>
       <c r="J94" s="3">
+        <v>-3312800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-3376400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2335200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3066500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1908500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2988300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2805200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4319400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>606900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2416900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2929600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4854000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4785300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3642300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3482200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4604300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3669900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3349400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4960500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4575200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2977700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3913400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5183400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4066000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6691400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3502400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8564,109 +8797,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-1552600</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-1510900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-1452900</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+        <v>1359300</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1469500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1432600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-1358600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-1464200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-1361900</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1472900</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1573100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1668500</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1564900</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1343800</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1093100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1084100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8766,8 +9003,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8867,8 +9107,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8968,307 +9211,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>3585800</v>
+        <v>-3081200</v>
       </c>
       <c r="E100" s="3">
-        <v>-3987000</v>
+        <v>3139500</v>
       </c>
       <c r="F100" s="3">
-        <v>1343600</v>
+        <v>-3712600</v>
       </c>
       <c r="G100" s="3">
-        <v>-1229800</v>
+        <v>1342500</v>
       </c>
       <c r="H100" s="3">
-        <v>2208600</v>
+        <v>-1159700</v>
       </c>
       <c r="I100" s="3">
-        <v>-5081600</v>
+        <v>2151400</v>
       </c>
       <c r="J100" s="3">
+        <v>-5384000</v>
+      </c>
+      <c r="K100" s="3">
         <v>287500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-118200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>697900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5668000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-258800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5545800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1634100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12979800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2024000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3087200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4957600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2601900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6920300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-102000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2742600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>115000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3031600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>138900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3545900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2541100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1473800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4333600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>616100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2694500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>120800</v>
+        <v>75100</v>
       </c>
       <c r="E101" s="3">
-        <v>133100</v>
+        <v>157800</v>
       </c>
       <c r="F101" s="3">
-        <v>-101500</v>
+        <v>22100</v>
       </c>
       <c r="G101" s="3">
-        <v>79700</v>
+        <v>-160000</v>
       </c>
       <c r="H101" s="3">
-        <v>162000</v>
+        <v>105000</v>
       </c>
       <c r="I101" s="3">
-        <v>20900</v>
+        <v>209100</v>
       </c>
       <c r="J101" s="3">
+        <v>129400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-149800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>97000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>191500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>104400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>44900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>15600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>10600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>119900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-50400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-16800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-75300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>60900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-32900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-76500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>36000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>31800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-71700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>24900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>13800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>51100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>88300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>932800</v>
+        <v>653400</v>
       </c>
       <c r="E102" s="3">
-        <v>268600</v>
+        <v>816700</v>
       </c>
       <c r="F102" s="3">
-        <v>1633300</v>
+        <v>250100</v>
       </c>
       <c r="G102" s="3">
-        <v>-2150600</v>
+        <v>1631900</v>
       </c>
       <c r="H102" s="3">
-        <v>1590300</v>
+        <v>-2028000</v>
       </c>
       <c r="I102" s="3">
-        <v>-198200</v>
+        <v>1549200</v>
       </c>
       <c r="J102" s="3">
+        <v>-210000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-901600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>153700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>607700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>54400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-541700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1687700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1496200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2957700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2540200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-515600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>332300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1392900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-478200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-859600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>690300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>362800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>176900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>859700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-889900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>124000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-669700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1540700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>776300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2309600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3101400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1283200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,133 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -807,86 +810,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>23333600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20526400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20684200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21468600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20854400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21594500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21260400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22730300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22185300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22940800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>23597900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26753500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27085300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27332100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26705400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>29643300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28339000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27316900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25931300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27821100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>27624000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>26057300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>25390800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>26880700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>25156800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>24903300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -968,29 +974,32 @@
       <c r="AC9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE9" s="3">
         <v>14315900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13646700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12122500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11756500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14418700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12033700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>11724700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1072,29 +1081,32 @@
       <c r="AC10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE10" s="3">
         <v>13505200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13977300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13934700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13634400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>12462000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13123100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>13178600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1131,8 +1143,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,8 +1355,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1365,86 +1384,89 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>152100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>164100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>147400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>608900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>171800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>188300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>638700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>328000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>203600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>184200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>886600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>316400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>277500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>207800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1326000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>957400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>300900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>243400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>167300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2970900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>332400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>246800</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1469,86 +1491,89 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3">
         <v>2807100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2498900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2626200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2677800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2667600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2791000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2811400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2735500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2782000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2910000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3141000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3330600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3326500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3323100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3302300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3296200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3154600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3074900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2958700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3108500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>6102700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5974800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5995600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3364800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3683200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>3208700</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1582,8 +1607,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1608,86 +1634,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>19611100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17379900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17291600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19948500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17210600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17823700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17686300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21531600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18566100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18960200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19353500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25769300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22825300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22942900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22077800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28041200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24030900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22360500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21047900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24898500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24267800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21413500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>20647900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>24918300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21679200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21008600</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1712,86 +1741,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>3722500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3146500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3392600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1520100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3643800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3770800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3574100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1198700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3619200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3980600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4244400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>984300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4260000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4389200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4627600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1602100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4308200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4956500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4883400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2922500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3356200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4643800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4742900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1962400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3477700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3894700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1828,8 +1860,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1854,86 +1887,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-98200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>149500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>83900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>56800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-28800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>73600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-82200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-27200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-19800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-82500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-15500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-23300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>197800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-242800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-40300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>19900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>49300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1123500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>78400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>103800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>79200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>236000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>190600</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1958,86 +1994,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>6431300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5650000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6168300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4281800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6368300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6533100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6459100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3852000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6373900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6870900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7377200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4232300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7571100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7689000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8127700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4655400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7422400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8051200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7891400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5939100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7548400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7734900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7838500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5406400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6963800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7254300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2062,8 +2101,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2101,8 +2140,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
@@ -2119,29 +2158,32 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>62500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>78700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>74500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>75300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>85100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>74400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2166,86 +2208,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>3624300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3151200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3542100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1604000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3700600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3742100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3647700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1116500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3591900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3960800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4236200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>901800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4244600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4365900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4825300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1359200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4267900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4976300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4932700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2841400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4401100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4647600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4771400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1956500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3639300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3998600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2270,86 +2315,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>1089100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>913300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>911600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>473200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1142600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1165700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1030900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>507000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1055300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1246800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1272500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>152100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1332200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1217500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1491500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>365800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1302600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1763500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1520700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>761900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1444900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1463800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1466700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>386100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1271900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1264100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2452,8 +2500,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2478,86 +2529,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>2535200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2237800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2630500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1130800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2558000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2576300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2616800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>609500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2536600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2714000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2963700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>749700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2912400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3148500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3333900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>993500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2965200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3212800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3412000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2079500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2956200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3183800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3304700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1570400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2367400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2734400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2582,86 +2636,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>2385000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2092900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2484200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2435500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2421400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2498900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>602700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2123200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2094500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2325600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>514400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2270700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2455000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2569700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>600000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2193900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2508100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2633800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1564900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2012000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2512900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2647500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1165500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1708600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2764,8 +2821,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,8 +2850,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2868,8 +2928,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2972,8 +3035,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3076,8 +3142,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3102,86 +3171,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>98200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-149500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-83900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-56800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>28800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-73600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>82200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>27200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>19800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>82500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>15500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>23300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-197800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>242800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>40300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-49300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>18700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1123500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-78400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-103800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-190600</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3206,86 +3278,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>2385000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2092900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2484200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2435500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2421400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2498900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>602700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2123200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2094500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2325600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>514400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2270700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2455000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2569700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>600000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2193900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2508100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2633800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1564900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2012000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2512900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2647500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1165500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1708600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3388,8 +3463,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3414,195 +3492,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>2385000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2092900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2484200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2435500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2421400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2498900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>602700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2123200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2094500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2325600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>514400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2270700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2455000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2569700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>600000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2193900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2508100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2633800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1564900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2012000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2512900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2647500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1165500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1708600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3639,8 +3723,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3677,112 +3762,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7621100</v>
+      </c>
+      <c r="E41" s="3">
         <v>8431000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6926600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6498100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6704300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4787100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7040200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5972300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5835000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6053500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6232700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5541500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5677100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6526600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8373800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6634300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9916700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7839400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9148700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9105800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7975500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8527900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9356900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9092300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8575100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8264800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7245700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15144700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6929900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7599600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8690400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8206600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5897100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8998400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3808,813 +3897,837 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>764600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>809700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>756300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>587200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>352000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>381600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>442400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>295900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4437100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>5884200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>305000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>285300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1174300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1041400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>998300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1131600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1158300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1087400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1160200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1401100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>398600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1303600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>786800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>566300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>677900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31728400</v>
+      </c>
+      <c r="E43" s="3">
         <v>30111900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27725200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31846600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31719400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28890500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26811700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>31492100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29066500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22712200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22451800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23936900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24668900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21499000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22885100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>25060000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27566200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25444000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27582500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>30860000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>41217200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>37411000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>38645800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>42201700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>39166800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>36843100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>34757800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>68781300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>31235300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>29446200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>26375400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>27995700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>29108000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>25063000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3687900</v>
+      </c>
+      <c r="E44" s="3">
         <v>4056600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3359200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3465400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3971300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3758500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3863500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3892200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3520300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3013100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2835300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2711500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2416000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2386300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2433500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2236400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2641700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2363200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2630700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2267100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2818000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2453800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2786700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3187000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4045200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3198000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3250000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6759800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4153400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3497200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3655500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3240900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3875200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3907300</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14764200</v>
+      </c>
+      <c r="E45" s="3">
         <v>13064500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13900100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13223300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8859000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8932000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10477600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8704800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8208700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7412500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7750300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5181000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4959400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4924400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5208500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3537400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4778900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4897300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17876500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>16539700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5436400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5317700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6432000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7620800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7330500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7113200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5420500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9493000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5634700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5426600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6214100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7111600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7980800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7524600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57801600</v>
+      </c>
+      <c r="E46" s="3">
         <v>55664000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>51911100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>55033500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>51254000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>46368100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48193000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>50061400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>47395100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40001000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40026400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37958200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>38073500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35717900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>39343300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>37764000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>49340600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46428000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>57543400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>59057800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>58621500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>54751800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>58219800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>63233500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>60275800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>56506500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>51834100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>53057200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>48351800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>47273300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>45722100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>47121200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>47539100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>46264000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2738900</v>
+      </c>
+      <c r="E47" s="3">
         <v>34125400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2640900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>33184900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>32103300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>29805800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29115400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29126000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13559100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12652700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13141700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12323600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13565400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14417400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>14328900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13662100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13548000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13074400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12768700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9951600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14218700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13411900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13511100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13807300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13538500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13687300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14984100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>23831700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>9577600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>9086300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8923400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8691600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8571600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8135900</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>72435600</v>
+      </c>
+      <c r="E48" s="3">
         <v>78980000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>71244700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>74952200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>76618500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>71768300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>72809000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>78502400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>80501300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>72543700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>76361000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>74753100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>77189000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>80463700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>82028500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>78731800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>79668500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>84222100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>91460600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>93742200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>95995400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>96175900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>95402300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>95907300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>92625800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>91769200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>89134300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>177505500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>87753100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>88621500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>87913000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>86207700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>84650400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>83893100</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27046700</v>
+      </c>
+      <c r="E49" s="3">
         <v>28930900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26911100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>27831000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27309200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>25587900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24370000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25624200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23685600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21308400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22061500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21014500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20859600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20768100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21166700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20008300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19726800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20619900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>22665300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23565900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24100000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23505500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23186600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>24162400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23906500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23809200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>23033500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>48621500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>26804000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>26981900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>26837400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>26415300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>25833000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>23543700</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4717,8 +4830,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4821,20 +4937,23 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>30222200</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
         <v>29217200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4847,86 +4966,89 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>13467100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12240300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12887800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12396000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12062300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12440600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12789200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12659100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12624700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13703800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15336600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16437000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16063700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16481200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16408400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17145900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16387700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16004400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>16148700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>30822500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>22127200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>22380200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22405700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>20054600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>19890900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5029,112 +5151,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>194653100</v>
+      </c>
+      <c r="E54" s="3">
         <v>202742900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>186424800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>195723900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>193277000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>179520700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>180731400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>190386600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>178608100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>158746100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>164478300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>158445300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>161749700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>163807600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>169656600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>162825300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>174908600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>178048300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>199774600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>202754500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>208999200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>204326400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>206728300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>214256400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>206734400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>201776600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>195134800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>194734700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>194613800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>194343300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>191801600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>188490400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>186485000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>181367100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5171,8 +5299,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5209,632 +5338,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15659500</v>
+      </c>
+      <c r="E57" s="3">
         <v>16650400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15515300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19443500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18119800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16178800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17378200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21117900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17652100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14193200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16106200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6541500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14575100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13308600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14666400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16709000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22680600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13558800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15530900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18877600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15531100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15365600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15442400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>20108700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15250500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13794100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13731500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>16378000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12341800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11209100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10462900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>14307300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10823200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10149200</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25663800</v>
+      </c>
+      <c r="E58" s="3">
         <v>20167500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22827600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18290100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21097000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15775000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19546600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15387000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19864800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15816300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15109700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12193000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14723800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16253200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>28766600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>23840300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>38403300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>18080500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21988600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>19458000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21904900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>16681400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>18869500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>13565300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15598300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>10476900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>14238400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15416900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8838000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8994300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9532100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>8191800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>9374100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>6176000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15177400</v>
+      </c>
+      <c r="E59" s="3">
         <v>15708300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14249300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16675800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9909300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9730100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9622800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10659600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11804600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11307500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11274200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22822800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10907200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11452200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10987400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12102100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10978900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12298300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17491000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19877400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13620000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14530600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14313800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16567700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14876600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15946100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14009300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>19934300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14207200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14711400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15808300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14146400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14897400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>13836100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>59493500</v>
+      </c>
+      <c r="E60" s="3">
         <v>56071700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55628600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>58475200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>52321600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45028600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>49650300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51431000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>49321500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41317000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>42490100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41557400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40206000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>41014000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>54420400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52651500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>72062700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43937600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>55010500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>58213100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>51055900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>46577600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>48625600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>50241800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>45725300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>40217100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>41979300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>41786800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>35387100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>34914900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>35803300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>36645500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>35094700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>30161200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51252600</v>
+      </c>
+      <c r="E61" s="3">
         <v>56105200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>49937900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52544000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54548300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51817100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>49665100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53448200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>47896900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>43865800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>44393900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42318000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45383600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>43143200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>36398100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>35517800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>25696600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19853800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23192800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22413700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29780700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29372500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29574300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>27844600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>27448700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27278100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>25389200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28423700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28726400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28965100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>29015900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28331200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>29049600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>30307400</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3320600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3794900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3486600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3571700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3634500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3859600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3212500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3841200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16060000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14264100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14949800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14689500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16384400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16927600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17223600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16496500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18169400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18967200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>20608700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21142000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22174100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22177200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21883800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>22726000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>22825400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>22206200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21740200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>40355000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21606000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21475400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21294000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>20989200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21797200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>21685400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5937,8 +6085,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6041,8 +6192,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6145,112 +6299,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>122904600</v>
+      </c>
+      <c r="E66" s="3">
         <v>125574900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>117618600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>123706100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>121480000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>111095300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>113038600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>120046200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>118789000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>104704400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>107091700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103449800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>106805100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106011600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>112803600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>109205700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>120390100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>102256800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>119437400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>122926200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>125660600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>121280500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>123114000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>125220500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>119475700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>114165700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>112192700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>112807400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>109849800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>108990500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>108974100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>108194900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>107689800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>103690600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6287,8 +6447,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6391,8 +6552,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6495,8 +6659,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6599,8 +6766,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6703,112 +6873,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60544500</v>
+      </c>
+      <c r="E72" s="3">
         <v>65935800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>56767600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>60018400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>61935000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57651700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57518400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>61309500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>55798600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49563300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>50164300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48431600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>47910400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>54408400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52990500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>50112200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>50282400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>53498600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>56283300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>57264500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>58586300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>58367600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>55697400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>57220900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>55878100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>54359500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>57216800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>55490700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>55074400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>54544700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>52229600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>49904000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>48738500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>48114000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6911,8 +7087,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7015,8 +7194,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7119,112 +7301,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64619000</v>
+      </c>
+      <c r="E76" s="3">
         <v>69737300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61965400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>65083200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>65508100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>62378000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>61883900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>64403000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59819100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54041700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57386700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>54995500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>54944700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>57796000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56853100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>53619600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>54518600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>75791500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>80337200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>79828300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>83338500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>83045900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>83614300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>89035800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>87258700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>87610900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>82942000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>81927300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>84764000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>85352800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>82827500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>80295500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>78795200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>77676600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7327,117 +7515,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7462,86 +7656,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>2385000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2092900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2484200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2435500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2421400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2498900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>602700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2123200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2094500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2325600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>514400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2270700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2455000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2569700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>600000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2193900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2508100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2633800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1564900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2012000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2512900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2647500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1165500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1708600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7578,112 +7775,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2887800</v>
+      </c>
+      <c r="E83" s="3">
         <v>2669100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2739900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3053800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2998100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2707000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2867300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3321000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2807100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2498900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2626200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2677800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2667600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2791000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2811400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2735500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2782000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2910000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3141000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3330600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3326500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3323100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3302300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3296200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3154600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3074900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2958700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3035200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3068600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3000700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3003800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3364800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3250100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3169000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7786,8 +7987,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7890,8 +8094,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7994,8 +8201,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8098,8 +8308,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8202,112 +8415,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-272100</v>
+      </c>
+      <c r="E89" s="3">
         <v>6465200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1213000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6225300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4303600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3247400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2357600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8464800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2337100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2510100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2784700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7526700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2660500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6647700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4170800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9295200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2983500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6301300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4112300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>11279800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1644300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9735800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4350900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7673800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3773500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7209000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3926000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7650900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6131900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5252800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4754300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10658100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2885700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7551100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8344,112 +8563,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3365300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3060200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3519100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4224000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3567800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2711400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3715400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4041300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-430425000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-357543000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-526691000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-463257000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400176000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-378841000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3790900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3311400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3036100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2832700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4693900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4336700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3957900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3333700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5192700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4354400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3592000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3450900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4247500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2610700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2900200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2538600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3781500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3982200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3701000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2945900</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8552,8 +8775,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8656,112 +8882,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3313100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2496900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3641700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2386500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3912700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4190800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3117700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3312800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3376400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2335200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3066500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1908500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2988300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2805200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4319400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>606900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2416900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2929600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4854000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4785300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3642300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3482200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4604300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3669900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3349400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4960500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4575200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2977700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3913400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5183400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4066000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-6691400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3502400</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8798,20 +9030,21 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>1387200</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>1359300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
@@ -8824,86 +9057,89 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>-1469500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1432600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1358600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1464200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1361900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1472900</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1573100</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1668500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1564900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1343800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1093100</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1084100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9006,8 +9242,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9110,8 +9349,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9214,316 +9456,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3311100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3081200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3139500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3712600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1342500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1159700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2151400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5384000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>287500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-118200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>697900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5668000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-258800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5545800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1634100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12979800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2024000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3087200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4957600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2601900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6920300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-102000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2742600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>115000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3031600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>138900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3545900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2541100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1473800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4333600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>616100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2694500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-101400</v>
+      </c>
+      <c r="E101" s="3">
         <v>75100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>157800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>22100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-160000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>105000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>209100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>129400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-149800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>97000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>191500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>104400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>44900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>15600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>10600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>119900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-50400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-16800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-75300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>60900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-32900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-76500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>36000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>31800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-71700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>24900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>13800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>51100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>88300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E102" s="3">
         <v>653400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>816700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>250100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1631900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2028000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1549200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-210000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-901600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>153700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>607700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>54400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-541700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1687700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1496200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2957700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2540200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-515600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>332300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1392900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-478200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-859600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>690300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>362800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>176900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>859700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-889900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>124000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-669700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1540700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>776300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2309600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3101400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1283200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,136 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -813,86 +816,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>23333600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20526400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20684200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21468600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20854400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21594500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21260400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22730300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22185300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22940800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>23597900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26753500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27085300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>27332100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26705400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>29643300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28339000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>27316900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>25931300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>27821100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>27624000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>26057300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>25390800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>26880700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>25156800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>24903300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -977,29 +983,32 @@
       <c r="AD9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF9" s="3">
         <v>14315900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13646700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12122500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11756500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14418700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>12033700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>11724700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1084,29 +1093,32 @@
       <c r="AD10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF10" s="3">
         <v>13505200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13977300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13934700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13634400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>12462000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>13123100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>13178600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1144,8 +1156,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1251,8 +1264,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,8 +1374,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,86 +1406,89 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>152100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>164100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>147400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>608900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>171800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>188300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>638700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>328000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>203600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>184200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>886600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>316400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>277500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>207800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1326000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>957400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>300900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>243400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>167300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2970900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>332400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>246800</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1494,86 +1516,89 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="3">
         <v>2807100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2498900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2626200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2677800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2667600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2791000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2811400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2735500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2782000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2910000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3141000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3330600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3326500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3323100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3302300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3296200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3154600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3074900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2958700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3108500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>6102700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5974800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5995600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3364800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>3683200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>3208700</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1608,8 +1633,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1637,86 +1663,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>19611100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17379900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17291600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19948500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17210600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17823700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17686300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21531600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18566100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18960200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>19353500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25769300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22825300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22942900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22077800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>28041200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24030900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22360500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21047900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24898500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24267800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21413500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>20647900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>24918300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21679200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>21008600</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1744,86 +1773,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>3722500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3146500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3392600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1520100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3643800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3770800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3574100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1198700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3619200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3980600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4244400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>984300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4260000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4389200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4627600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1602100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4308200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4956500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4883400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2922500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3356200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4643800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4742900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1962400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3477700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3894700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1861,8 +1893,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1890,86 +1923,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-98200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>149500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>83900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>56800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-28800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>73600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-82200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-27200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-82500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>197800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-242800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-40300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>19900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>49300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1123500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>78400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>103800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>79200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>236000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>190600</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1997,86 +2033,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>6431300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5650000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6168300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4281800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6368300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6533100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6459100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3852000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6373900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6870900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7377200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4232300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7571100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7689000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8127700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4655400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7422400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8051200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7891400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5939100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7548400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7734900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7838500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>5406400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6963800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>7254300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2104,8 +2143,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2143,8 +2182,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
@@ -2161,29 +2200,32 @@
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="3">
         <v>62500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>78700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>74500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>75300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>85100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>74400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2211,86 +2253,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>3624300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3151200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3542100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1604000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3700600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3742100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3647700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1116500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3591900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3960800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4236200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>901800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4244600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4365900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4825300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1359200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4267900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4976300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4932700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2841400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4401100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4647600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4771400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1956500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3639300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3998600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2318,86 +2363,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>1089100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>913300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>911600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>473200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1142600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1165700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1030900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>507000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1055300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1246800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1272500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>152100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1332200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1217500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1491500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>365800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1302600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1763500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1520700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>761900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1444900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1463800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1466700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>386100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1271900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1264100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2551,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2532,86 +2583,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>2535200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2237800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2630500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1130800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2558000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2576300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2616800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>609500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2536600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2714000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2963700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>749700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2912400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3148500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3333900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>993500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2965200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3212800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3412000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2079500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2956200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3183800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3304700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1570400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2367400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2734400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2639,86 +2693,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>2385000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2092900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2484200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2435500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2421400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2498900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>602700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2123200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2094500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2325600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>514400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2270700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2455000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2569700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>600000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2193900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2508100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2633800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1564900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2012000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2512900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2647500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1165500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1708600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2824,8 +2881,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2853,8 +2913,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2931,8 +2991,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3038,8 +3101,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3145,8 +3211,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3174,86 +3243,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>98200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-149500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-83900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-56800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>28800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-73600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>82200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>27200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>82500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>15500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>23300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-197800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>242800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>40300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-49300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>18700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1123500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-78400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-103800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-190600</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3281,86 +3353,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>2385000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2092900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2484200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2435500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2421400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2498900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>602700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2123200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2094500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2325600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>514400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2270700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2455000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2569700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>600000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2193900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2508100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2633800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1564900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2012000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2512900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2647500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1165500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1708600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3466,8 +3541,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3495,198 +3573,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>2385000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2092900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2484200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2435500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2421400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2498900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>602700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2123200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2094500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2325600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>514400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2270700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2455000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2569700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>600000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2193900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2508100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2633800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1564900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2012000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2512900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2647500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1165500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1708600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3724,8 +3808,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3763,115 +3848,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6684500</v>
+      </c>
+      <c r="E41" s="3">
         <v>7621100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8431000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6926600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6498100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6704300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4787100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7040200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5972300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5835000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6053500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6232700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5541500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5677100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6526600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8373800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6634300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9916700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7839400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9148700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9105800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7975500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8527900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9356900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9092300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8575100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8264800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7245700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>15144700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6929900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7599600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8690400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8206600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5897100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8998400</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3900,834 +3989,858 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>764600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>809700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>756300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>587200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>352000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>381600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>442400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>295900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4437100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5884200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>305000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>285300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1174300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1041400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>998300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1131600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1158300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1087400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1160200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1401100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>398600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1303600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>786800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>566300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>677900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32593200</v>
+      </c>
+      <c r="E43" s="3">
         <v>31728400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30111900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27725200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31846600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31719400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28890500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26811700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>31492100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29066500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22712200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22451800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23936900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24668900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21499000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>22885100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>25060000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27566200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>25444000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27582500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>30860000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>41217200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>37411000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>38645800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>42201700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>39166800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>36843100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>34757800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>68781300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>31235300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>29446200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>26375400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>27995700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>29108000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>25063000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3716800</v>
+      </c>
+      <c r="E44" s="3">
         <v>3687900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4056600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3359200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3465400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3971300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3758500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3863500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3892200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3520300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3013100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2835300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2711500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2416000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2386300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2433500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2236400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2641700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2363200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2630700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2267100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2818000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2453800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2786700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3187000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4045200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3198000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3250000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6759800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4153400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3497200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3655500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3240900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3875200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3907300</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12901800</v>
+      </c>
+      <c r="E45" s="3">
         <v>14764200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13064500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13900100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13223300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8859000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8932000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10477600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8704800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8208700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7412500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7750300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5181000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4959400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4924400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5208500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3537400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4778900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4897300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17876500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>16539700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5436400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5317700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6432000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7620800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7330500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7113200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5420500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9493000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5634700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5426600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>6214100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7111600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7980800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7524600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55896300</v>
+      </c>
+      <c r="E46" s="3">
         <v>57801600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55664000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>51911100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>55033500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>51254000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>46368100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48193000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50061400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>47395100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40001000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>40026400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37958200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>38073500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35717900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>39343300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>37764000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>49340600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46428000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>57543400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>59057800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>58621500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>54751800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>58219800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>63233500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>60275800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>56506500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>51834100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>53057200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>48351800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>47273300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>45722100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>47121200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>47539100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>46264000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3019100</v>
+      </c>
+      <c r="E47" s="3">
         <v>2738900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34125400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2640900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>33184900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>32103300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29805800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29115400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29126000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13559100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12652700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13141700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12323600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13565400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>14417400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14328900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13662100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13548000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13074400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12768700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9951600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>14218700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13411900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13511100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13807300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13538500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13687300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>14984100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>23831700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>9577600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>9086300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8923400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8691600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8571600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8135900</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>77706000</v>
+      </c>
+      <c r="E48" s="3">
         <v>72435600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>78980000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>71244700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>74952200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>76618500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>71768300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>72809000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>78502400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>80501300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>72543700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>76361000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>74753100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>77189000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>80463700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>82028500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>78731800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>79668500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>84222100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>91460600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>93742200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>95995400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>96175900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>95402300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>95907300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>92625800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>91769200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>89134300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>177505500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>87753100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>88621500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>87913000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>86207700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>84650400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>83893100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28063100</v>
+      </c>
+      <c r="E49" s="3">
         <v>27046700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>28930900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26911100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27831000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>27309200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>25587900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24370000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25624200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23685600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21308400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22061500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>21014500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20859600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20768100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>21166700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>20008300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19726800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>20619900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>22665300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23565900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24100000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23505500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23186600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>24162400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23906500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>23809200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>23033500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>48621500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>26804000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>26981900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>26837400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>26415300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>25833000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>23543700</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4833,8 +4946,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4940,23 +5056,26 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>31625300</v>
+      </c>
+      <c r="E52" s="3">
         <v>30222200</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>29217200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4969,86 +5088,89 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>13467100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12240300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12887800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12396000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12062300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12440600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12789200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12659100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12624700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13703800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15336600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16437000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16063700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16481200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16408400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>17145900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16387700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>16004400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16148700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>30822500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>22127200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22380200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>22405700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>20054600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>19890900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5154,115 +5276,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>200753800</v>
+      </c>
+      <c r="E54" s="3">
         <v>194653100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>202742900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>186424800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>195723900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>193277000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>179520700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>180731400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>190386600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>178608100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>158746100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>164478300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>158445300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>161749700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>163807600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>169656600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>162825300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>174908600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>178048300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>199774600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>202754500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>208999200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>204326400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>206728300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>214256400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>206734400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>201776600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>195134800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>194734700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>194613800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>194343300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>191801600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>188490400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>186485000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>181367100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5300,8 +5428,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5339,650 +5468,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19028900</v>
+      </c>
+      <c r="E57" s="3">
         <v>15659500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16650400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15515300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19443500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18119800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16178800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17378200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21117900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17652100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14193200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16106200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6541500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14575100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13308600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14666400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16709000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>22680600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13558800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15530900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>18877600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15531100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15365600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15442400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>20108700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15250500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13794100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13731500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>16378000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12341800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11209100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10462900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>14307300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10823200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>10149200</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20395900</v>
+      </c>
+      <c r="E58" s="3">
         <v>25663800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20167500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22827600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18290100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21097000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15775000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19546600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15387000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19864800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15816300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15109700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12193000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14723800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16253200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>28766600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>23840300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>38403300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>18080500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21988600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>19458000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21904900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>16681400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>18869500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>13565300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15598300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>10476900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>14238400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>15416900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8838000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8994300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>9532100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>8191800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>9374100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6176000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15813100</v>
+      </c>
+      <c r="E59" s="3">
         <v>15177400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15708300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14249300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16675800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9909300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9730100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9622800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10659600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11804600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11307500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11274200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22822800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10907200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11452200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10987400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12102100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10978900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12298300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17491000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>19877400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13620000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14530600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14313800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16567700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14876600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15946100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14009300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19934300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14207200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14711400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>15808300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14146400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14897400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13836100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>59201200</v>
+      </c>
+      <c r="E60" s="3">
         <v>59493500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>56071700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55628600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>58475200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>52321600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45028600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>49650300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51431000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>49321500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41317000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>42490100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41557400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40206000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>41014000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>54420400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>52651500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>72062700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43937600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>55010500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>58213100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>51055900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>46577600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>48625600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>50241800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>45725300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>40217100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>41979300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>41786800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>35387100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>34914900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>35803300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>36645500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>35094700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30161200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54204200</v>
+      </c>
+      <c r="E61" s="3">
         <v>51252600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>56105200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>49937900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52544000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54548300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51817100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>49665100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53448200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47896900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43865800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>44393900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42318000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45383600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>43143200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>36398100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>35517800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>25696600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19853800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23192800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22413700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29780700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29372500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29574300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>27844600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27448700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>27278100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25389200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28423700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28726400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28965100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>29015900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28331200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>29049600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>30307400</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3599600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3320600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3794900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3486600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3571700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3634500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3859600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3212500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3841200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16060000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14264100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14949800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14689500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16384400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16927600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17223600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16496500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18169400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18967200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20608700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21142000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22174100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22177200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>21883800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>22726000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>22825400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>22206200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21740200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>40355000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21606000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21475400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21294000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>20989200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>21797200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>21685400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6088,8 +6236,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6195,8 +6346,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6302,115 +6456,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>124995600</v>
+      </c>
+      <c r="E66" s="3">
         <v>122904600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>125574900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>117618600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>123706100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>121480000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>111095300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>113038600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>120046200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>118789000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>104704400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>107091700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>103449800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106805100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>106011600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>112803600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>109205700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>120390100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>102256800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>119437400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>122926200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>125660600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>121280500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>123114000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>125220500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>119475700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>114165700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>112192700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>112807400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>109849800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>108990500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>108974100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>108194900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>107689800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>103690600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6448,8 +6608,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6555,8 +6716,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6662,8 +6826,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6769,8 +6936,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6876,115 +7046,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>64951600</v>
+      </c>
+      <c r="E72" s="3">
         <v>60544500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>65935800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56767600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>60018400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>61935000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57651700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>57518400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>61309500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>55798600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49563300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>50164300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48431600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>47910400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>54408400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52990500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>50112200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50282400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>53498600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>56283300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>57264500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>58586300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>58367600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>55697400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>57220900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>55878100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>54359500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>57216800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>55490700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>55074400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>54544700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>52229600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>49904000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>48738500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>48114000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7090,8 +7266,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7197,8 +7376,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7304,115 +7486,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>68258600</v>
+      </c>
+      <c r="E76" s="3">
         <v>64619000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>69737300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>61965400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>65083200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>65508100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>62378000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>61883900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>64403000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>59819100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>54041700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>57386700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>54995500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>54944700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>57796000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>56853100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>53619600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>54518600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>75791500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>80337200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>79828300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>83338500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>83045900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>83614300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>89035800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>87258700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>87610900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>82942000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>81927300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>84764000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>85352800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>82827500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>80295500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>78795200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>77676600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7518,120 +7706,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7659,86 +7853,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>2385000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2092900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2484200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2435500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2421400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2498900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>602700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2123200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2094500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2325600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>514400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2270700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2455000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2569700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>600000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2193900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2508100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2633800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1564900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2012000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2512900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2647500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1165500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1708600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7776,115 +7973,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2821100</v>
+      </c>
+      <c r="E83" s="3">
         <v>2887800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2669100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2739900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3053800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2998100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2707000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2867300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3321000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2807100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2498900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2626200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2677800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2667600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2791000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2811400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2735500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2782000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2910000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3141000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3330600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3326500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3323100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3302300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3296200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3154600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3074900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2958700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3035200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3068600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3000700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3003800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3364800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3250100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3169000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7990,8 +8191,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8097,8 +8301,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8204,8 +8411,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8311,8 +8521,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8418,115 +8631,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8584100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-272100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6465200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1213000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6225300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4303600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3247400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2357600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8464800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2337100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2510100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2784700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7526700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2660500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6647700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4170800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9295200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2983500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6301300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4112300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11279800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1644300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9735800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4350900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7673800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3773500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7209000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3926000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7650900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6131900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5252800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4754300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10658100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2885700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>7551100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8564,115 +8783,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3998000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3365300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3060200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3519100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4224000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3567800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2711400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3715400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4041300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-430425000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-357543000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-526691000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-463257000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400176000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-378841000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3790900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3311400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3036100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2832700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4693900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4336700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3957900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3333700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5192700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4354400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3592000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3450900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4247500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2610700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2900200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2538600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3781500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3982200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3701000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2945900</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8778,8 +9001,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8885,115 +9111,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3574200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3313100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2496900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3641700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2386500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3912700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4190800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3117700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3312800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3376400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2335200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3066500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1908500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2988300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2805200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4319400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>606900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2416900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2929600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4854000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4785300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3642300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3482200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4604300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3669900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3349400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4960500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4575200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2977700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3913400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5183400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4066000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6691400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3502400</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9031,23 +9263,24 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1387200</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>1359300</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
@@ -9060,86 +9293,89 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1469500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-1432600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-1358600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-1464200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1361900</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1472900</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1573100</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1668500</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1564900</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1343800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1093100</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-1084100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9245,8 +9481,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9352,8 +9591,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9459,325 +9701,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6191900</v>
+      </c>
+      <c r="E100" s="3">
         <v>3311100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3081200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3139500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3712600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1342500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1159700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2151400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5384000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>287500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-118200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>697900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5668000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-258800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5545800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1634100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12979800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2024000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3087200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4957600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2601900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6920300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2742600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>115000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3031600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>138900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3545900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2541100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1473800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4333600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>616100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2694500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-101400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>75100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>157800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>22100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-160000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>105000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>209100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>129400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-149800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>97000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>191500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>104400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>44900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>15600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>10600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>119900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-50400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-16800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-75300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>60900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-32900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-76500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>36000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>31800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-71700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>24900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>13800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>88300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1316800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-61600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>653400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>816700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>250100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1631900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2028000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1549200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-210000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-901600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>153700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>607700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>54400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-541700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1687700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1496200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2957700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2540200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-515600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>332300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1392900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-478200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-859600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>690300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>362800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>176900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>859700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-889900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>124000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-669700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1540700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>776300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2309600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3101400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1283200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTTYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="92">
   <si>
     <t>NTTYY</t>
   </si>
@@ -656,139 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,86 +827,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>23333600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20526400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20684200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21468600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20854400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21594500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21260400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22730300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22185300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22940800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23597900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26753500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>27085300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27332100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>26705400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>29643300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28339000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27316900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>25931300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>27821100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>27624000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>26057300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>25390800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>26880700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>25156800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>24903300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -986,29 +997,32 @@
       <c r="AE9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG9" s="3">
         <v>14315900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>13646700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12122500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>11756500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14418700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>12033700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>11724700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1096,29 +1110,32 @@
       <c r="AE10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG10" s="3">
         <v>13505200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13977300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13934700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13634400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>12462000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>13123100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>13178600</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1157,8 +1174,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1267,8 +1285,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,8 +1398,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,86 +1433,89 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>152100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>164100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>147400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>608900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>171800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>188300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>638700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>328000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>203600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>184200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>886600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>316400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>277500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>207800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1326000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>957400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>300900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>243400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>167300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2970900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>332400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>246800</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1519,86 +1546,89 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3">
         <v>2807100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2498900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2626200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2677800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2667600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2791000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2811400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2735500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2782000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2910000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3141000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3330600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3326500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3323100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3302300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3296200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3154600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3074900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2958700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3108500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>6102700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5974800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>5995600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>3364800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>3683200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>3208700</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1634,8 +1664,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1666,86 +1697,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>19611100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17379900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17291600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19948500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17210600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17823700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17686300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21531600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18566100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18960200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19353500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>25769300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22825300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22942900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22077800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>28041200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24030900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22360500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21047900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24898500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>24267800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21413500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>20647900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>24918300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>21679200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>21008600</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1776,86 +1810,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>3722500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3146500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3392600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1520100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3643800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3770800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3574100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1198700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3619200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3980600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4244400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>984300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4260000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4389200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4627600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1602100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4308200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4956500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4883400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2922500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3356200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4643800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4742900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1962400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3477700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3894700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1894,8 +1931,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1926,86 +1964,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-98200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>149500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>83900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>56800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-28800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>73600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-82200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-27200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-19800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-82500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>197800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-242800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-40300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>19900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>49300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1123500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>78400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>103800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>79200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>236000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>190600</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2036,86 +2077,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>6431300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5650000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6168300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4281800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6368300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6533100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6459100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3852000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6373900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6870900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7377200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4232300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7571100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7689000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8127700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4655400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7422400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8051200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7891400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5939100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7548400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7734900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7838500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5406400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6963800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7254300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2146,8 +2190,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2185,8 +2229,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
@@ -2203,29 +2247,32 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3">
         <v>62500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>78700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>74500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>75300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>85100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>74400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2256,86 +2303,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>3624300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3151200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3542100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1604000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3700600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3742100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3647700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1116500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3591900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3960800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4236200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>901800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4244600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4365900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4825300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1359200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4267900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4976300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4932700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2841400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4401100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4647600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4771400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1956500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3639300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3998600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2366,86 +2416,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>1089100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>913300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>911600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>473200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1142600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1165700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1030900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>507000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1055300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1246800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1272500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>152100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1332200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1217500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1491500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>365800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1302600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1763500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1520700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>761900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1444900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1463800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1466700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>386100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1271900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1264100</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,8 +2607,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2586,86 +2642,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>2535200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2237800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2630500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1130800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2558000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2576300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2616800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>609500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2536600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2714000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2963700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>749700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2912400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3148500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3333900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>993500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2965200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3212800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3412000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2079500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2956200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3183800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3304700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1570400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2367400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2734400</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2696,86 +2755,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>2385000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2092900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2484200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1000900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2435500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2421400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2498900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>602700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2123200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2094500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2325600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>514400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2270700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2455000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2569700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>600000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2193900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2508100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2633800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1564900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2012000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2512900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2647500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1165500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1708600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2884,8 +2946,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2916,8 +2981,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2994,8 +3059,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3104,8 +3172,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3214,8 +3285,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3246,86 +3320,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>98200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-149500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-83900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-56800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>28800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-73600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>82200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>27200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>19800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>82500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>15500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>23300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-197800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>242800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>40300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-49300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>18700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1123500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-78400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-103800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-190600</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3356,86 +3433,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>2385000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2092900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2484200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1000900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2435500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2421400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2498900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>602700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2123200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2094500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2325600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>514400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2270700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2455000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2569700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>600000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2193900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2508100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2633800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1564900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2012000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2512900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2647500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1165500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1708600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3544,8 +3624,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3576,201 +3659,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>2385000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2092900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2484200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1000900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2435500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2421400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2498900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>602700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2123200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2094500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2325600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>514400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2270700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2455000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2569700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>600000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2193900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2508100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2633800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1564900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2012000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2512900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2647500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1165500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1708600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3809,8 +3898,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3849,118 +3939,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>6684500</v>
       </c>
-      <c r="E41" s="3">
-        <v>7621100</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>8431000</v>
       </c>
-      <c r="G41" s="3">
-        <v>6926600</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>6498100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6704300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4787100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7040200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5972300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5835000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6053500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6232700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5541500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5677100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6526600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8373800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6634300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9916700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7839400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9148700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9105800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7975500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8527900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9356900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9092300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8575100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8264800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7245700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>15144700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6929900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7599600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8690400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8206600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5897100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8998400</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3992,855 +4086,879 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>764600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>809700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>756300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>587200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>352000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>381600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>442400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>295900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4437100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5884200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>305000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>285300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1174300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1041400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>998300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1131600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1158300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1087400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1160200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1401100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>398600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1303600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>786800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>566300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>677900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>32593200</v>
       </c>
-      <c r="E43" s="3">
-        <v>31728400</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>30111900</v>
       </c>
-      <c r="G43" s="3">
-        <v>27725200</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>31846600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>31719400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28890500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26811700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>31492100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29066500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22712200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22451800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23936900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24668900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21499000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>22885100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25060000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27566200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>25444000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27582500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>30860000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>41217200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>37411000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>38645800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>42201700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>39166800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>36843100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>34757800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>68781300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>31235300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>29446200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>26375400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>27995700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>29108000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>25063000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>3716800</v>
       </c>
-      <c r="E44" s="3">
-        <v>3687900</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>4056600</v>
       </c>
-      <c r="G44" s="3">
-        <v>3359200</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>3465400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3971300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3758500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3863500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3892200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3520300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3013100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2835300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2711500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2416000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2386300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2433500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2236400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2641700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2363200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2630700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2267100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2818000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2453800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2786700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3187000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4045200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3198000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3250000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6759800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4153400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3497200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3655500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3240900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3875200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3907300</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>12901800</v>
       </c>
-      <c r="E45" s="3">
-        <v>14764200</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>13064500</v>
       </c>
-      <c r="G45" s="3">
-        <v>13900100</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>13223300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8859000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8932000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10477600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8704800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8208700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7412500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7750300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5181000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4959400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4924400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5208500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3537400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4778900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4897300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17876500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>16539700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5436400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5317700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6432000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7620800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7330500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7113200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5420500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>9493000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5634700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5426600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>6214100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7111600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7980800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>7524600</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>55896300</v>
       </c>
-      <c r="E46" s="3">
-        <v>57801600</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>55664000</v>
       </c>
-      <c r="G46" s="3">
-        <v>51911100</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
         <v>55033500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51254000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46368100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48193000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>50061400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>47395100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>40001000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>40026400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37958200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>38073500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>35717900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>39343300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37764000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>49340600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>46428000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>57543400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>59057800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>58621500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>54751800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>58219800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>63233500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>60275800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>56506500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>51834100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>53057200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>48351800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>47273300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>45722100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>47121200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>47539100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>46264000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>3019100</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>2738900</v>
-      </c>
-      <c r="F47" s="3">
+        <v>34644500</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>34125400</v>
       </c>
-      <c r="G47" s="3">
-        <v>2640900</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>33184900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32103300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29805800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29115400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29126000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13559100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12652700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13141700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12323600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13565400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14417400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14328900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13662100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13548000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13074400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12768700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9951600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14218700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13411900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13511100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13807300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13538500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13687300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>14984100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>23831700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>9577600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>9086300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8923400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8691600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8571600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>8135900</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>77706000</v>
       </c>
-      <c r="E48" s="3">
-        <v>72435600</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>78980000</v>
       </c>
-      <c r="G48" s="3">
-        <v>71244700</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>74952200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>76618500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>71768300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72809000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>78502400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>80501300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>72543700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>76361000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>74753100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>77189000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>80463700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>82028500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>78731800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>79668500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>84222100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>91460600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>93742200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>95995400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>96175900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>95402300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>95907300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>92625800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>91769200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>89134300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>177505500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>87753100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>88621500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>87913000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>86207700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>84650400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>83893100</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
         <v>28063100</v>
       </c>
-      <c r="E49" s="3">
-        <v>27046700</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
         <v>28930900</v>
       </c>
-      <c r="G49" s="3">
-        <v>26911100</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
         <v>27831000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27309200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25587900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24370000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25624200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23685600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21308400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22061500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>21014500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20859600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20768100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>21166700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20008300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19726800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>20619900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>22665300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23565900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24100000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23505500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23186600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>24162400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>23906500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>23809200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>23033500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>48621500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>26804000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>26981900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>26837400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>26415300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>25833000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>23543700</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4949,8 +5067,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5059,22 +5180,25 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>31625300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>30222200</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>29217200</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
@@ -5091,86 +5215,89 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>13467100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12240300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12887800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12396000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12062300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12440600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12789200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12659100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12624700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>13703800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15336600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16437000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16063700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16481200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16408400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17145900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>16387700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16004400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>16148700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>30822500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22127200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>22380200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>22405700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>20054600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>19890900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>19530300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5279,118 +5406,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>200753800</v>
       </c>
-      <c r="E54" s="3">
-        <v>194653100</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>202742900</v>
       </c>
-      <c r="G54" s="3">
-        <v>186424800</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>195723900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>193277000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>179520700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>180731400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>190386600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>178608100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>158746100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>164478300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>158445300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>161749700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>163807600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>169656600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>162825300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>174908600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>178048300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>199774600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>202754500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>208999200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>204326400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>206728300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>214256400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>206734400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>201776600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>195134800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>194734700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>194613800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>194343300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>191801600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>188490400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>186485000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>181367100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5429,8 +5562,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5469,668 +5603,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>19028900</v>
       </c>
-      <c r="E57" s="3">
-        <v>15659500</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>16650400</v>
       </c>
-      <c r="G57" s="3">
-        <v>15515300</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>19443500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18119800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16178800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17378200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>21117900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17652100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14193200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16106200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6541500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14575100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13308600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14666400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16709000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>22680600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13558800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15530900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>18877600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15531100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15365600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15442400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>20108700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>15250500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13794100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13731500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>16378000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12341800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11209100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10462900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>14307300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>10823200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>10149200</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>20395900</v>
       </c>
-      <c r="E58" s="3">
-        <v>25663800</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>20167500</v>
       </c>
-      <c r="G58" s="3">
-        <v>22827600</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
         <v>18290100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21097000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15775000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19546600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15387000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19864800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15816300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15109700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12193000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14723800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>16253200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>28766600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>23840300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>38403300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>18080500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21988600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19458000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21904900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>16681400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>18869500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>13565300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15598300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10476900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>14238400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>15416900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8838000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>8994300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>9532100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>8191800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>9374100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6176000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>15813100</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>15177400</v>
-      </c>
-      <c r="F59" s="3">
+        <v>15783700</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>15708300</v>
       </c>
-      <c r="G59" s="3">
-        <v>14249300</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>16675800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9909300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9730100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9622800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10659600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11804600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11307500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11274200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22822800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10907200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11452200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10987400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12102100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10978900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12298300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17491000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>19877400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13620000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14530600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14313800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>16567700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14876600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15946100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14009300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>19934300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14207200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14711400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>15808300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14146400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>14897400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13836100</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>59201200</v>
+      <c r="D60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E60" s="3">
-        <v>59493500</v>
-      </c>
-      <c r="F60" s="3">
+        <v>59171800</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>56071700</v>
       </c>
-      <c r="G60" s="3">
-        <v>55628600</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>58475200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52321600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>45028600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>49650300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51431000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>49321500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41317000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>42490100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>41557400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>40206000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>41014000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>54420400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>52651500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>72062700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43937600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>55010500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>58213100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>51055900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>46577600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>48625600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>50241800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>45725300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>40217100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>41979300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>41786800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>35387100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>34914900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>35803300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>36645500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>35094700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>30161200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>54204200</v>
       </c>
-      <c r="E61" s="3">
-        <v>51252600</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>56105200</v>
       </c>
-      <c r="G61" s="3">
-        <v>49937900</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>52544000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>54548300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51817100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>49665100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>53448200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47896900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43865800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>44393900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42318000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45383600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>43143200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>36398100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>35517800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>25696600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19853800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>23192800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22413700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29780700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29372500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>29574300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27844600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>27448700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>27278100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>25389200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28423700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28726400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28965100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>29015900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>28331200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>29049600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>30307400</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>3599600</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
-        <v>3320600</v>
-      </c>
-      <c r="F62" s="3">
+        <v>3629100</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>3794900</v>
       </c>
-      <c r="G62" s="3">
-        <v>3486600</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>3571700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3634500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3859600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3212500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3841200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16060000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14264100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14949800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14689500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16384400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16927600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17223600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16496500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18169400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18967200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>20608700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21142000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22174100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>22177200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>21883800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>22726000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>22825400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>22206200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21740200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>40355000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21606000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21475400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21294000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>20989200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>21797200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>21685400</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6239,8 +6392,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6349,8 +6505,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6459,118 +6618,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>124995600</v>
       </c>
-      <c r="E66" s="3">
-        <v>122904600</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>125574900</v>
       </c>
-      <c r="G66" s="3">
-        <v>117618600</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>123706100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>121480000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>111095300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>113038600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>120046200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>118789000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>104704400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>107091700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>103449800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>106805100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>106011600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>112803600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>109205700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>120390100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>102256800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>119437400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>122926200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>125660600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>121280500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>123114000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>125220500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>119475700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>114165700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>112192700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>112807400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>109849800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>108990500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>108974100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>108194900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>107689800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>103690600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6609,8 +6774,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6719,8 +6885,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6829,8 +6998,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6939,8 +7111,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7049,118 +7224,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>64951600</v>
       </c>
-      <c r="E72" s="3">
-        <v>60544500</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>65935800</v>
       </c>
-      <c r="G72" s="3">
-        <v>56767600</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>60018400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>61935000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>57651700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57518400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>61309500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>55798600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>49563300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50164300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>48431600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47910400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>54408400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>52990500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50112200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>50282400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>53498600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>56283300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>57264500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>58586300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>58367600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>55697400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>57220900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>55878100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>54359500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>57216800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>55490700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>55074400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>54544700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>52229600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>49904000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>48738500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>48114000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7269,8 +7450,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7379,8 +7563,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7489,118 +7676,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>68258600</v>
       </c>
-      <c r="E76" s="3">
-        <v>64619000</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>69737300</v>
       </c>
-      <c r="G76" s="3">
-        <v>61965400</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>65083200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>65508100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>62378000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>61883900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>64403000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>59819100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>54041700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>57386700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>54995500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>54944700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>57796000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>56853100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>53619600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>54518600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>75791500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>80337200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>79828300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>83338500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>83045900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>83614300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>89035800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>87258700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>87610900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>82942000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>81927300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>84764000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>85352800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>82827500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>80295500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>78795200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>77676600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7709,123 +7902,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7856,86 +8055,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>2385000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2092900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2484200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1000900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2435500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2421400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2498900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>602700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2123200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2094500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2325600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>514400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2270700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2455000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2569700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>600000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2193900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2508100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2633800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1564900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2012000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2512900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2647500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1165500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1708600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2062000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7974,118 +8176,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>2821100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2887800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2669100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2739900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3053800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2998100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2707000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2867300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3321000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2807100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2498900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2626200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2677800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2667600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2791000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2811400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2735500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2782000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2910000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3141000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3330600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3326500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3323100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3302300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3296200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3154600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3074900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2958700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3035200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3068600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3000700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3003800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3364800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3250100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>3169000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8194,8 +8400,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8304,8 +8513,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8414,8 +8626,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8524,8 +8739,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8634,118 +8852,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>8584100</v>
       </c>
-      <c r="E89" s="3">
-        <v>-272100</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>6465200</v>
       </c>
-      <c r="G89" s="3">
-        <v>1213000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>6225300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4303600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3247400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2357600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8464800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2337100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2510100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2784700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7526700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2660500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6647700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4170800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9295200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2983500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6301300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4112300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11279800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1644300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9735800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4350900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7673800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3773500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7209000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3926000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7650900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6131900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5252800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4754300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>10658100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2885700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>7551100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8784,118 +9008,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3998000</v>
       </c>
-      <c r="E91" s="3">
-        <v>-3365300</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-3060200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-3519100</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-4224000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3567800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2711400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3715400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4041300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-430425000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-357543000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-526691000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-463257000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400176000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-378841000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3790900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3311400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3036100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2832700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4693900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4336700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3957900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3333700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5192700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4354400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3592000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3450900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4247500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2610700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2900200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2538600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3781500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3982200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3701000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2945900</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9004,8 +9232,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9114,118 +9345,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3574200</v>
       </c>
-      <c r="E94" s="3">
-        <v>-3313100</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-2496900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-3641700</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2386500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3912700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4190800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3117700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3312800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3376400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2335200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3066500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1908500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2988300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2805200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4319400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>606900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2416900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2929600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4854000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4785300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3642300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3482200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4604300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3669900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3349400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4960500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4575200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2977700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3913400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5183400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4066000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-6691400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3502400</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9264,22 +9501,23 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>1387200</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>1359300</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
@@ -9296,86 +9534,89 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1469500</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1432600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1358600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1464200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1361900</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1472900</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1573100</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1668500</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1564900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1343800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1360400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1093100</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-1084100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9484,8 +9725,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9594,8 +9838,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9704,334 +9951,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6191900</v>
       </c>
-      <c r="E100" s="3">
-        <v>3311100</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-3081200</v>
       </c>
-      <c r="G100" s="3">
-        <v>3139500</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-3712600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1342500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1159700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2151400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5384000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>287500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-118200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>697900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5668000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-258800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5545800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1634100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12979800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2024000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3087200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4957600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2601900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6920300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2742600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>115000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3031600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>138900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3545900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3809000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2541100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1473800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4333600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>616100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2694500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>123900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-101400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>75100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>157800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-160000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>105000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>209100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>129400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-149800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>97000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>191500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>104400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>44900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>15600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>119900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-50400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-16800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-75300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>60900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-32900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-76500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>36000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>31800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-71700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>24900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>13800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>51100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>88300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-71000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1316800</v>
       </c>
-      <c r="E102" s="3">
-        <v>-61600</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>653400</v>
       </c>
-      <c r="G102" s="3">
-        <v>816700</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>250100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1631900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2028000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1549200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-210000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-901600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>153700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>607700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>54400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-541700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1687700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1496200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2957700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2540200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-515600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>332300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1392900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-478200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-859600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>690300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>362800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>176900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>859700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-889900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>124000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-669700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1540700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>776300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2309600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-3101400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1283200</v>
       </c>
     </row>
